--- a/02_Imputation/c_data/10_imputation_supp.xlsx
+++ b/02_Imputation/c_data/10_imputation_supp.xlsx
@@ -7644,7 +7644,7 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0869565217391304</v>
+        <v>0.0859570214892554</v>
       </c>
     </row>
     <row r="8">
@@ -7667,7 +7667,7 @@
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0499750124937531</v>
+        <v>0.0514742628685657</v>
       </c>
     </row>
     <row r="9">
@@ -7713,7 +7713,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.000499750124937531</v>
+        <v>0.000999500249875062</v>
       </c>
     </row>
     <row r="11">
@@ -7736,7 +7736,7 @@
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0904547726136932</v>
+        <v>0.0994502748625687</v>
       </c>
     </row>
     <row r="12">
@@ -7845,7 +7845,7 @@
         <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>0.378310844577711</v>
+        <v>0.370814592703648</v>
       </c>
     </row>
     <row r="17">
@@ -7889,7 +7889,7 @@
         <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>0.649175412293853</v>
+        <v>0.63968015992004</v>
       </c>
     </row>
     <row r="19">
@@ -7933,7 +7933,7 @@
         <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0119940029985007</v>
+        <v>0.0184907546226887</v>
       </c>
     </row>
     <row r="21">
@@ -7979,7 +7979,7 @@
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>0.107946026986507</v>
+        <v>0.116941529235382</v>
       </c>
     </row>
     <row r="23">
@@ -8086,7 +8086,7 @@
         <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>0.24687656171914</v>
+        <v>0.228885557221389</v>
       </c>
     </row>
     <row r="28">
@@ -8174,7 +8174,7 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0624687656171914</v>
+        <v>0.0599700149925037</v>
       </c>
     </row>
     <row r="32">
@@ -8218,7 +8218,7 @@
         <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0134932533733133</v>
+        <v>0.0119940029985007</v>
       </c>
     </row>
     <row r="34">
@@ -8367,7 +8367,7 @@
         <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>0.47376311844078</v>
+        <v>0.476261869065467</v>
       </c>
     </row>
     <row r="41">
@@ -8432,7 +8432,7 @@
         <v>1</v>
       </c>
       <c r="G43" t="n">
-        <v>0.11344327836082</v>
+        <v>0.122938530734633</v>
       </c>
     </row>
     <row r="44">
@@ -8518,7 +8518,7 @@
         <v>1</v>
       </c>
       <c r="G47" t="n">
-        <v>0.00599700149925037</v>
+        <v>0.00199900049975012</v>
       </c>
     </row>
     <row r="48">
@@ -8541,7 +8541,7 @@
         <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>0.063968015992004</v>
+        <v>0.0544727636181909</v>
       </c>
     </row>
     <row r="49">
@@ -8692,7 +8692,7 @@
         <v>1</v>
       </c>
       <c r="G55" t="n">
-        <v>0.0469765117441279</v>
+        <v>0.047976011994003</v>
       </c>
     </row>
     <row r="56">
@@ -8736,7 +8736,7 @@
         <v>1</v>
       </c>
       <c r="G57" t="n">
-        <v>0.782608695652174</v>
+        <v>0.802598700649675</v>
       </c>
     </row>
     <row r="58">
@@ -8759,7 +8759,7 @@
         <v>1</v>
       </c>
       <c r="G58" t="n">
-        <v>0.752623688155922</v>
+        <v>0.737131434282859</v>
       </c>
     </row>
     <row r="59">
@@ -8868,7 +8868,7 @@
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>0.0149925037481259</v>
+        <v>0.0139930034982509</v>
       </c>
     </row>
     <row r="64">
@@ -8998,7 +8998,7 @@
         <v>1</v>
       </c>
       <c r="G69" t="n">
-        <v>0.0304847576211894</v>
+        <v>0.0324837581209395</v>
       </c>
     </row>
     <row r="70">
@@ -9021,7 +9021,7 @@
         <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>0.000499750124937531</v>
+        <v>0.000999500249875062</v>
       </c>
     </row>
     <row r="71">
@@ -9086,7 +9086,7 @@
         <v>1</v>
       </c>
       <c r="G73" t="n">
-        <v>0.255872063968016</v>
+        <v>0.254372813593203</v>
       </c>
     </row>
     <row r="74">
@@ -9109,7 +9109,7 @@
         <v>1</v>
       </c>
       <c r="G74" t="n">
-        <v>0.851574212893553</v>
+        <v>0.865567216391804</v>
       </c>
     </row>
     <row r="75">
@@ -9176,7 +9176,7 @@
         <v>1</v>
       </c>
       <c r="G77" t="n">
-        <v>0.172913543228386</v>
+        <v>0.19240379810095</v>
       </c>
     </row>
     <row r="78">
@@ -9199,7 +9199,7 @@
         <v>1</v>
       </c>
       <c r="G78" t="n">
-        <v>0.184407796101949</v>
+        <v>0.186406796601699</v>
       </c>
     </row>
     <row r="79">
@@ -9222,7 +9222,7 @@
         <v>1</v>
       </c>
       <c r="G79" t="n">
-        <v>0.00899550224887556</v>
+        <v>0.00349825087456272</v>
       </c>
     </row>
     <row r="80">
@@ -9268,7 +9268,7 @@
         <v>1</v>
       </c>
       <c r="G81" t="n">
-        <v>0.1984007996002</v>
+        <v>0.178910544727636</v>
       </c>
     </row>
     <row r="82">
@@ -9291,7 +9291,7 @@
         <v>1</v>
       </c>
       <c r="G82" t="n">
-        <v>0.623688155922039</v>
+        <v>0.60519740129935</v>
       </c>
     </row>
     <row r="83">
@@ -9314,7 +9314,7 @@
         <v>1</v>
       </c>
       <c r="G83" t="n">
-        <v>0.180409795102449</v>
+        <v>0.186406796601699</v>
       </c>
     </row>
     <row r="84">
@@ -9337,7 +9337,7 @@
         <v>1</v>
       </c>
       <c r="G84" t="n">
-        <v>0.0899550224887556</v>
+        <v>0.0764617691154423</v>
       </c>
     </row>
     <row r="85">
@@ -9383,7 +9383,7 @@
         <v>1</v>
       </c>
       <c r="G86" t="n">
-        <v>0.0384807596201899</v>
+        <v>0.0409795102448776</v>
       </c>
     </row>
     <row r="87">
@@ -9406,7 +9406,7 @@
         <v>1</v>
       </c>
       <c r="G87" t="n">
-        <v>0.324837581209395</v>
+        <v>0.32383808095952</v>
       </c>
     </row>
     <row r="88">
@@ -9450,7 +9450,7 @@
         <v>1</v>
       </c>
       <c r="G89" t="n">
-        <v>0.0189905047476262</v>
+        <v>0.0169915042478761</v>
       </c>
     </row>
     <row r="90">
@@ -9494,7 +9494,7 @@
         <v>1</v>
       </c>
       <c r="G91" t="n">
-        <v>0.0194902548725637</v>
+        <v>0.0109945027486257</v>
       </c>
     </row>
     <row r="92">
@@ -9584,7 +9584,7 @@
         <v>1</v>
       </c>
       <c r="G95" t="n">
-        <v>0.0184907546226887</v>
+        <v>0.0179910044977511</v>
       </c>
     </row>
     <row r="96">
@@ -9714,7 +9714,7 @@
         <v>0</v>
       </c>
       <c r="G101" t="n">
-        <v>0.00549725137431284</v>
+        <v>0.0079960019990005</v>
       </c>
     </row>
     <row r="102">
@@ -9867,7 +9867,7 @@
         <v>1</v>
       </c>
       <c r="G108" t="n">
-        <v>0.0804597701149425</v>
+        <v>0.0849575212393803</v>
       </c>
     </row>
     <row r="109">
@@ -9934,7 +9934,7 @@
         <v>1</v>
       </c>
       <c r="G111" t="n">
-        <v>0.0369815092453773</v>
+        <v>0.0289855072463768</v>
       </c>
     </row>
     <row r="112">
@@ -9978,7 +9978,7 @@
         <v>1</v>
       </c>
       <c r="G113" t="n">
-        <v>0.495752123938031</v>
+        <v>0.492753623188406</v>
       </c>
     </row>
     <row r="114">
@@ -10022,7 +10022,7 @@
         <v>1</v>
       </c>
       <c r="G115" t="n">
-        <v>0.734132933533233</v>
+        <v>0.738130934532734</v>
       </c>
     </row>
     <row r="116">
@@ -10173,7 +10173,7 @@
         <v>1</v>
       </c>
       <c r="G122" t="n">
-        <v>0.015992003998001</v>
+        <v>0.0114942528735632</v>
       </c>
     </row>
     <row r="123">
@@ -10196,7 +10196,7 @@
         <v>1</v>
       </c>
       <c r="G123" t="n">
-        <v>0.233883058470765</v>
+        <v>0.235882058970515</v>
       </c>
     </row>
     <row r="124">
@@ -10219,7 +10219,7 @@
         <v>1</v>
       </c>
       <c r="G124" t="n">
-        <v>0.174912543728136</v>
+        <v>0.168415792103948</v>
       </c>
     </row>
     <row r="125">
@@ -10242,7 +10242,7 @@
         <v>1</v>
       </c>
       <c r="G125" t="n">
-        <v>0.111944027986007</v>
+        <v>0.0994502748625687</v>
       </c>
     </row>
     <row r="126">
@@ -10286,7 +10286,7 @@
         <v>1</v>
       </c>
       <c r="G127" t="n">
-        <v>0.00199900049975012</v>
+        <v>0.000999500249875062</v>
       </c>
     </row>
     <row r="128">
@@ -10330,7 +10330,7 @@
         <v>1</v>
       </c>
       <c r="G129" t="n">
-        <v>0.326336831584208</v>
+        <v>0.346826586706647</v>
       </c>
     </row>
     <row r="130">
@@ -10418,7 +10418,7 @@
         <v>1</v>
       </c>
       <c r="G133" t="n">
-        <v>0.0794602698650675</v>
+        <v>0.0814592703648176</v>
       </c>
     </row>
     <row r="134">
@@ -10441,7 +10441,7 @@
         <v>1</v>
       </c>
       <c r="G134" t="n">
-        <v>0.301349325337331</v>
+        <v>0.344827586206897</v>
       </c>
     </row>
     <row r="135">
@@ -10506,7 +10506,7 @@
         <v>1</v>
       </c>
       <c r="G137" t="n">
-        <v>0.0424787606196902</v>
+        <v>0.0459770114942529</v>
       </c>
     </row>
     <row r="138">
@@ -10592,7 +10592,7 @@
         <v>1</v>
       </c>
       <c r="G141" t="n">
-        <v>0.321339330334833</v>
+        <v>0.303848075962019</v>
       </c>
     </row>
     <row r="142">
@@ -10701,7 +10701,7 @@
         <v>0</v>
       </c>
       <c r="G146" t="n">
-        <v>0.0294852573713143</v>
+        <v>0.0314842578710645</v>
       </c>
     </row>
     <row r="147">
@@ -10747,7 +10747,7 @@
         <v>0</v>
       </c>
       <c r="G148" t="n">
-        <v>0.00749625187406297</v>
+        <v>0.00849575212393803</v>
       </c>
     </row>
     <row r="149">
@@ -10984,7 +10984,7 @@
         <v>1</v>
       </c>
       <c r="G159" t="n">
-        <v>0.00249875062468766</v>
+        <v>0.00199900049975012</v>
       </c>
     </row>
     <row r="160">
@@ -11007,7 +11007,7 @@
         <v>1</v>
       </c>
       <c r="G160" t="n">
-        <v>0.186406796601699</v>
+        <v>0.191904047976012</v>
       </c>
     </row>
     <row r="161">
@@ -11135,7 +11135,7 @@
         <v>1</v>
       </c>
       <c r="G166" t="n">
-        <v>0.376311844077961</v>
+        <v>0.370314842578711</v>
       </c>
     </row>
     <row r="167">
@@ -11158,7 +11158,7 @@
         <v>1</v>
       </c>
       <c r="G167" t="n">
-        <v>0.293853073463268</v>
+        <v>0.289855072463768</v>
       </c>
     </row>
     <row r="168">
@@ -11181,7 +11181,7 @@
         <v>1</v>
       </c>
       <c r="G168" t="n">
-        <v>0.00549725137431284</v>
+        <v>0.00499750124937531</v>
       </c>
     </row>
     <row r="169">
@@ -11288,7 +11288,7 @@
         <v>1</v>
       </c>
       <c r="G173" t="n">
-        <v>0.173913043478261</v>
+        <v>0.163418290854573</v>
       </c>
     </row>
     <row r="174">
@@ -11332,7 +11332,7 @@
         <v>1</v>
       </c>
       <c r="G175" t="n">
-        <v>0.190904547726137</v>
+        <v>0.174412793603198</v>
       </c>
     </row>
     <row r="176">
@@ -11355,7 +11355,7 @@
         <v>1</v>
       </c>
       <c r="G176" t="n">
-        <v>0.158420789605197</v>
+        <v>0.151424287856072</v>
       </c>
     </row>
     <row r="177">
@@ -11464,7 +11464,7 @@
         <v>1</v>
       </c>
       <c r="G181" t="n">
-        <v>0.047976011994003</v>
+        <v>0.0459770114942529</v>
       </c>
     </row>
     <row r="182">
@@ -11508,7 +11508,7 @@
         <v>1</v>
       </c>
       <c r="G183" t="n">
-        <v>0.193903048475762</v>
+        <v>0.182908545727136</v>
       </c>
     </row>
     <row r="184">
@@ -11615,7 +11615,7 @@
         <v>1</v>
       </c>
       <c r="G188" t="n">
-        <v>0.0194902548725637</v>
+        <v>0.0219890054972514</v>
       </c>
     </row>
     <row r="189">
@@ -11659,7 +11659,7 @@
         <v>1</v>
       </c>
       <c r="G190" t="n">
-        <v>0.157421289355322</v>
+        <v>0.15992003998001</v>
       </c>
     </row>
     <row r="191">
@@ -11791,7 +11791,7 @@
         <v>1</v>
       </c>
       <c r="G196" t="n">
-        <v>0.116941529235382</v>
+        <v>0.11344327836082</v>
       </c>
     </row>
     <row r="197">
@@ -11837,7 +11837,7 @@
         <v>1</v>
       </c>
       <c r="G198" t="n">
-        <v>0.591704147926037</v>
+        <v>0.615692153923038</v>
       </c>
     </row>
     <row r="199">
@@ -11860,7 +11860,7 @@
         <v>1</v>
       </c>
       <c r="G199" t="n">
-        <v>0.145927036481759</v>
+        <v>0.168415792103948</v>
       </c>
     </row>
     <row r="200">
@@ -11946,7 +11946,7 @@
         <v>1</v>
       </c>
       <c r="G203" t="n">
-        <v>0.000499750124937531</v>
+        <v>0.000999500249875062</v>
       </c>
     </row>
     <row r="204">
@@ -11990,7 +11990,7 @@
         <v>1</v>
       </c>
       <c r="G205" t="n">
-        <v>0.04047976011994</v>
+        <v>0.0444777611194403</v>
       </c>
     </row>
     <row r="206">
@@ -12097,7 +12097,7 @@
         <v>1</v>
       </c>
       <c r="G210" t="n">
-        <v>0.968515742128936</v>
+        <v>0.96751624187906</v>
       </c>
     </row>
     <row r="211">
@@ -12162,7 +12162,7 @@
         <v>1</v>
       </c>
       <c r="G213" t="n">
-        <v>0.144427786106947</v>
+        <v>0.125937031484258</v>
       </c>
     </row>
     <row r="214">
@@ -12294,7 +12294,7 @@
         <v>1</v>
       </c>
       <c r="G219" t="n">
-        <v>0.47976011994003</v>
+        <v>0.493753123438281</v>
       </c>
     </row>
     <row r="220">
@@ -12317,7 +12317,7 @@
         <v>1</v>
       </c>
       <c r="G220" t="n">
-        <v>0.0324837581209395</v>
+        <v>0.0364817591204398</v>
       </c>
     </row>
     <row r="221">
@@ -12384,7 +12384,7 @@
         <v>1</v>
       </c>
       <c r="G223" t="n">
-        <v>0.176911544227886</v>
+        <v>0.185407296351824</v>
       </c>
     </row>
     <row r="224">
@@ -12407,7 +12407,7 @@
         <v>1</v>
       </c>
       <c r="G224" t="n">
-        <v>0.711144427786107</v>
+        <v>0.714142928535732</v>
       </c>
     </row>
     <row r="225">
@@ -12430,7 +12430,7 @@
         <v>1</v>
       </c>
       <c r="G225" t="n">
-        <v>0.178410794602699</v>
+        <v>0.181409295352324</v>
       </c>
     </row>
     <row r="226">
@@ -12453,7 +12453,7 @@
         <v>1</v>
       </c>
       <c r="G226" t="n">
-        <v>0.611694152923538</v>
+        <v>0.597701149425287</v>
       </c>
     </row>
     <row r="227">
@@ -12497,7 +12497,7 @@
         <v>1</v>
       </c>
       <c r="G228" t="n">
-        <v>0.00149925037481259</v>
+        <v>0.000999500249875062</v>
       </c>
     </row>
     <row r="229">
@@ -12564,7 +12564,7 @@
         <v>1</v>
       </c>
       <c r="G231" t="n">
-        <v>0.0454772613693153</v>
+        <v>0.047976011994003</v>
       </c>
     </row>
     <row r="232">
@@ -12587,7 +12587,7 @@
         <v>0</v>
       </c>
       <c r="G232" t="n">
-        <v>0.00199900049975012</v>
+        <v>0.000999500249875062</v>
       </c>
     </row>
     <row r="233">
@@ -12631,7 +12631,7 @@
         <v>1</v>
       </c>
       <c r="G234" t="n">
-        <v>0.0739630184907546</v>
+        <v>0.0789605197401299</v>
       </c>
     </row>
     <row r="235">
@@ -12654,7 +12654,7 @@
         <v>1</v>
       </c>
       <c r="G235" t="n">
-        <v>0.000999500249875062</v>
+        <v>0.000499750124937531</v>
       </c>
     </row>
     <row r="236">
@@ -12698,7 +12698,7 @@
         <v>1</v>
       </c>
       <c r="G237" t="n">
-        <v>0.0864567716141929</v>
+        <v>0.0904547726136932</v>
       </c>
     </row>
     <row r="238">
@@ -12786,7 +12786,7 @@
         <v>1</v>
       </c>
       <c r="G241" t="n">
-        <v>0.0194902548725637</v>
+        <v>0.0169915042478761</v>
       </c>
     </row>
     <row r="242">
@@ -12832,7 +12832,7 @@
         <v>1</v>
       </c>
       <c r="G243" t="n">
-        <v>0.0464767616191904</v>
+        <v>0.0574712643678161</v>
       </c>
     </row>
     <row r="244">
@@ -12878,7 +12878,7 @@
         <v>0</v>
       </c>
       <c r="G245" t="n">
-        <v>0.00399800099950025</v>
+        <v>0.00149925037481259</v>
       </c>
     </row>
     <row r="246">
@@ -12901,7 +12901,7 @@
         <v>1</v>
       </c>
       <c r="G246" t="n">
-        <v>0.819590204897551</v>
+        <v>0.800599700149925</v>
       </c>
     </row>
     <row r="247">
@@ -12945,7 +12945,7 @@
         <v>0</v>
       </c>
       <c r="G248" t="n">
-        <v>0.000999500249875062</v>
+        <v>0.00199900049975012</v>
       </c>
     </row>
     <row r="249">
@@ -12968,7 +12968,7 @@
         <v>1</v>
       </c>
       <c r="G249" t="n">
-        <v>0.0379810094952524</v>
+        <v>0.0304847576211894</v>
       </c>
     </row>
     <row r="250">
@@ -13014,7 +13014,7 @@
         <v>1</v>
       </c>
       <c r="G251" t="n">
-        <v>0.0064967516241879</v>
+        <v>0.00899550224887556</v>
       </c>
     </row>
     <row r="252">
@@ -13037,7 +13037,7 @@
         <v>1</v>
       </c>
       <c r="G252" t="n">
-        <v>0.0374812593703148</v>
+        <v>0.0414792603698151</v>
       </c>
     </row>
     <row r="253">
@@ -13188,7 +13188,7 @@
         <v>1</v>
       </c>
       <c r="G259" t="n">
-        <v>0.0569715142428786</v>
+        <v>0.0519740129935032</v>
       </c>
     </row>
     <row r="260">
@@ -13232,7 +13232,7 @@
         <v>1</v>
       </c>
       <c r="G261" t="n">
-        <v>0.15792103948026</v>
+        <v>0.144927536231884</v>
       </c>
     </row>
     <row r="262">
@@ -13276,7 +13276,7 @@
         <v>1</v>
       </c>
       <c r="G263" t="n">
-        <v>0.0139930034982509</v>
+        <v>0.0124937531234383</v>
       </c>
     </row>
     <row r="264">
@@ -13429,7 +13429,7 @@
         <v>1</v>
       </c>
       <c r="G270" t="n">
-        <v>0.164417791104448</v>
+        <v>0.152923538230885</v>
       </c>
     </row>
     <row r="271">
@@ -13561,7 +13561,7 @@
         <v>1</v>
       </c>
       <c r="G276" t="n">
-        <v>0.0439780109945027</v>
+        <v>0.0424787606196902</v>
       </c>
     </row>
     <row r="277">
@@ -13649,7 +13649,7 @@
         <v>1</v>
       </c>
       <c r="G280" t="n">
-        <v>0.535732133933034</v>
+        <v>0.544227886056971</v>
       </c>
     </row>
     <row r="281">
@@ -13672,7 +13672,7 @@
         <v>1</v>
       </c>
       <c r="G281" t="n">
-        <v>0.00149925037481259</v>
+        <v>0.000999500249875062</v>
       </c>
     </row>
     <row r="282">
@@ -13718,7 +13718,7 @@
         <v>1</v>
       </c>
       <c r="G283" t="n">
-        <v>0.867066466766617</v>
+        <v>0.871064467766117</v>
       </c>
     </row>
     <row r="284">
@@ -13934,7 +13934,7 @@
         <v>1</v>
       </c>
       <c r="G293" t="n">
-        <v>0.372313843078461</v>
+        <v>0.358820589705147</v>
       </c>
     </row>
     <row r="294">
@@ -13980,7 +13980,7 @@
         <v>1</v>
       </c>
       <c r="G295" t="n">
-        <v>0.147426286856572</v>
+        <v>0.177911044477761</v>
       </c>
     </row>
     <row r="296">
@@ -14135,7 +14135,7 @@
         <v>1</v>
       </c>
       <c r="G302" t="n">
-        <v>0.00149925037481259</v>
+        <v>0.00199900049975012</v>
       </c>
     </row>
     <row r="303">
@@ -14267,7 +14267,7 @@
         <v>1</v>
       </c>
       <c r="G308" t="n">
-        <v>0.774612693653173</v>
+        <v>0.799100449775112</v>
       </c>
     </row>
     <row r="309">
@@ -14311,7 +14311,7 @@
         <v>1</v>
       </c>
       <c r="G310" t="n">
-        <v>0.191404297851074</v>
+        <v>0.187406296851574</v>
       </c>
     </row>
     <row r="311">
@@ -14397,7 +14397,7 @@
         <v>1</v>
       </c>
       <c r="G314" t="n">
-        <v>0.567716141929036</v>
+        <v>0.531734132933533</v>
       </c>
     </row>
     <row r="315">
@@ -14630,7 +14630,7 @@
         <v>0</v>
       </c>
       <c r="G325" t="n">
-        <v>0.00299850074962519</v>
+        <v>0.00249875062468766</v>
       </c>
     </row>
     <row r="326">
@@ -14928,7 +14928,7 @@
         <v>1</v>
       </c>
       <c r="G339" t="n">
-        <v>0.00449775112443778</v>
+        <v>0.00699650174912544</v>
       </c>
     </row>
     <row r="340">
@@ -14951,7 +14951,7 @@
         <v>1</v>
       </c>
       <c r="G340" t="n">
-        <v>0.618690654672664</v>
+        <v>0.602698650674663</v>
       </c>
     </row>
     <row r="341">
@@ -14974,7 +14974,7 @@
         <v>1</v>
       </c>
       <c r="G341" t="n">
-        <v>0.0779610194902549</v>
+        <v>0.0769615192403798</v>
       </c>
     </row>
     <row r="342">
@@ -15125,7 +15125,7 @@
         <v>1</v>
       </c>
       <c r="G348" t="n">
-        <v>0.489755122438781</v>
+        <v>0.478760619690155</v>
       </c>
     </row>
     <row r="349">
@@ -15320,7 +15320,7 @@
         <v>1</v>
       </c>
       <c r="G357" t="n">
-        <v>0.23288355822089</v>
+        <v>0.232383808095952</v>
       </c>
     </row>
     <row r="358">
@@ -15343,7 +15343,7 @@
         <v>1</v>
       </c>
       <c r="G358" t="n">
-        <v>0.325337331334333</v>
+        <v>0.317341329335332</v>
       </c>
     </row>
     <row r="359">
@@ -15408,7 +15408,7 @@
         <v>1</v>
       </c>
       <c r="G361" t="n">
-        <v>0.241879060469765</v>
+        <v>0.250374812593703</v>
       </c>
     </row>
     <row r="362">
@@ -15958,7 +15958,7 @@
         <v>1</v>
       </c>
       <c r="G387" t="n">
-        <v>0.24487756121939</v>
+        <v>0.254872563718141</v>
       </c>
     </row>
     <row r="388">
@@ -16044,7 +16044,7 @@
         <v>1</v>
       </c>
       <c r="G391" t="n">
-        <v>0.0154922538730635</v>
+        <v>0.0169915042478761</v>
       </c>
     </row>
     <row r="392">
@@ -16176,7 +16176,7 @@
         <v>1</v>
       </c>
       <c r="G397" t="n">
-        <v>0.0474762618690655</v>
+        <v>0.0429785107446277</v>
       </c>
     </row>
     <row r="398">
@@ -16222,7 +16222,7 @@
         <v>1</v>
       </c>
       <c r="G399" t="n">
-        <v>0.015992003998001</v>
+        <v>0.0269865067466267</v>
       </c>
     </row>
     <row r="400">
@@ -16289,7 +16289,7 @@
         <v>1</v>
       </c>
       <c r="G402" t="n">
-        <v>0.149425287356322</v>
+        <v>0.152923538230885</v>
       </c>
     </row>
     <row r="403">
@@ -16375,7 +16375,7 @@
         <v>1</v>
       </c>
       <c r="G406" t="n">
-        <v>0.00249875062468766</v>
+        <v>0.000999500249875062</v>
       </c>
     </row>
     <row r="407">
@@ -16545,7 +16545,7 @@
         <v>1</v>
       </c>
       <c r="G414" t="n">
-        <v>0.900049975012494</v>
+        <v>0.91704147926037</v>
       </c>
     </row>
     <row r="415">
@@ -16589,7 +16589,7 @@
         <v>1</v>
       </c>
       <c r="G416" t="n">
-        <v>0.251874062968516</v>
+        <v>0.242378810594703</v>
       </c>
     </row>
     <row r="417">
@@ -16635,7 +16635,7 @@
         <v>1</v>
       </c>
       <c r="G418" t="n">
-        <v>0.0539730134932534</v>
+        <v>0.0594702648675662</v>
       </c>
     </row>
     <row r="419">
@@ -16679,7 +16679,7 @@
         <v>1</v>
       </c>
       <c r="G420" t="n">
-        <v>0.00349825087456272</v>
+        <v>0.0064967516241879</v>
       </c>
     </row>
     <row r="421">
@@ -16723,7 +16723,7 @@
         <v>1</v>
       </c>
       <c r="G422" t="n">
-        <v>0.633183408295852</v>
+        <v>0.596201899050475</v>
       </c>
     </row>
     <row r="423">
@@ -16832,7 +16832,7 @@
         <v>1</v>
       </c>
       <c r="G427" t="n">
-        <v>0.0119940029985007</v>
+        <v>0.00849575212393803</v>
       </c>
     </row>
     <row r="428">
@@ -16939,7 +16939,7 @@
         <v>0</v>
       </c>
       <c r="G432" t="n">
-        <v>0.0184907546226887</v>
+        <v>0.0149925037481259</v>
       </c>
     </row>
     <row r="433">
@@ -16962,7 +16962,7 @@
         <v>1</v>
       </c>
       <c r="G433" t="n">
-        <v>0.127936031984008</v>
+        <v>0.130934532733633</v>
       </c>
     </row>
     <row r="434">
@@ -17029,7 +17029,7 @@
         <v>0</v>
       </c>
       <c r="G436" t="n">
-        <v>0.00299850074962519</v>
+        <v>0.00199900049975012</v>
       </c>
     </row>
     <row r="437">
@@ -17199,7 +17199,7 @@
         <v>1</v>
       </c>
       <c r="G444" t="n">
-        <v>0.48575712143928</v>
+        <v>0.500249875062469</v>
       </c>
     </row>
     <row r="445">
@@ -17287,7 +17287,7 @@
         <v>1</v>
       </c>
       <c r="G448" t="n">
-        <v>0.6071964017991</v>
+        <v>0.613193403298351</v>
       </c>
     </row>
     <row r="449">
@@ -17354,7 +17354,7 @@
         <v>1</v>
       </c>
       <c r="G451" t="n">
-        <v>0.116941529235382</v>
+        <v>0.11744127936032</v>
       </c>
     </row>
     <row r="452">
@@ -17398,7 +17398,7 @@
         <v>1</v>
       </c>
       <c r="G453" t="n">
-        <v>0.247876061969015</v>
+        <v>0.234382808595702</v>
       </c>
     </row>
     <row r="454">
@@ -17505,7 +17505,7 @@
         <v>1</v>
       </c>
       <c r="G458" t="n">
-        <v>0.0199900049975013</v>
+        <v>0.0224887556221889</v>
       </c>
     </row>
     <row r="459">
@@ -17549,7 +17549,7 @@
         <v>1</v>
       </c>
       <c r="G460" t="n">
-        <v>0.0169915042478761</v>
+        <v>0.0209895052473763</v>
       </c>
     </row>
     <row r="461">
@@ -17700,7 +17700,7 @@
         <v>1</v>
       </c>
       <c r="G467" t="n">
-        <v>0.168915542228886</v>
+        <v>0.160919540229885</v>
       </c>
     </row>
     <row r="468">
@@ -17828,7 +17828,7 @@
         <v>1</v>
       </c>
       <c r="G473" t="n">
-        <v>0.00549725137431284</v>
+        <v>0.00349825087456272</v>
       </c>
     </row>
     <row r="474">
@@ -17851,7 +17851,7 @@
         <v>1</v>
       </c>
       <c r="G474" t="n">
-        <v>0.0189905047476262</v>
+        <v>0.0259870064967516</v>
       </c>
     </row>
     <row r="475">
@@ -18023,7 +18023,7 @@
         <v>1</v>
       </c>
       <c r="G482" t="n">
-        <v>0.000499750124937531</v>
+        <v>0.000999500249875062</v>
       </c>
     </row>
     <row r="483">
@@ -18046,7 +18046,7 @@
         <v>1</v>
       </c>
       <c r="G483" t="n">
-        <v>0.0384807596201899</v>
+        <v>0.0474762618690655</v>
       </c>
     </row>
     <row r="484">
@@ -18090,7 +18090,7 @@
         <v>1</v>
       </c>
       <c r="G485" t="n">
-        <v>0.831584207896052</v>
+        <v>0.823588205897052</v>
       </c>
     </row>
     <row r="486">
@@ -18113,7 +18113,7 @@
         <v>1</v>
       </c>
       <c r="G486" t="n">
-        <v>0.452273863068466</v>
+        <v>0.451774112943528</v>
       </c>
     </row>
     <row r="487">
@@ -18201,7 +18201,7 @@
         <v>1</v>
       </c>
       <c r="G490" t="n">
-        <v>0.00749625187406297</v>
+        <v>0.00349825087456272</v>
       </c>
     </row>
     <row r="491">
@@ -18266,7 +18266,7 @@
         <v>1</v>
       </c>
       <c r="G493" t="n">
-        <v>0.0434782608695652</v>
+        <v>0.0469765117441279</v>
       </c>
     </row>
     <row r="494">
@@ -18289,7 +18289,7 @@
         <v>1</v>
       </c>
       <c r="G494" t="n">
-        <v>0.00299850074962519</v>
+        <v>0.00349825087456272</v>
       </c>
     </row>
     <row r="495">
@@ -18564,7 +18564,7 @@
         <v>1</v>
       </c>
       <c r="G507" t="n">
-        <v>0.144427786106947</v>
+        <v>0.16191904047976</v>
       </c>
     </row>
     <row r="508">
@@ -18715,7 +18715,7 @@
         <v>1</v>
       </c>
       <c r="G514" t="n">
-        <v>0.0624687656171914</v>
+        <v>0.0629685157421289</v>
       </c>
     </row>
     <row r="515">
@@ -18803,7 +18803,7 @@
         <v>1</v>
       </c>
       <c r="G518" t="n">
-        <v>0.00349825087456272</v>
+        <v>0.00199900049975012</v>
       </c>
     </row>
     <row r="519">
@@ -18935,7 +18935,7 @@
         <v>1</v>
       </c>
       <c r="G524" t="n">
-        <v>0.493753123438281</v>
+        <v>0.506246876561719</v>
       </c>
     </row>
     <row r="525">
@@ -18979,7 +18979,7 @@
         <v>1</v>
       </c>
       <c r="G526" t="n">
-        <v>0.856071964017991</v>
+        <v>0.858570714642679</v>
       </c>
     </row>
     <row r="527">
@@ -19023,7 +19023,7 @@
         <v>1</v>
       </c>
       <c r="G528" t="n">
-        <v>0.60519740129935</v>
+        <v>0.605697151424288</v>
       </c>
     </row>
     <row r="529">
@@ -19067,7 +19067,7 @@
         <v>0</v>
       </c>
       <c r="G530" t="n">
-        <v>0.000999500249875062</v>
+        <v>0.00149925037481259</v>
       </c>
     </row>
     <row r="531">
@@ -19178,7 +19178,7 @@
         <v>1</v>
       </c>
       <c r="G535" t="n">
-        <v>0.0279860069965017</v>
+        <v>0.0219890054972514</v>
       </c>
     </row>
     <row r="536">
@@ -19495,7 +19495,7 @@
         <v>1</v>
       </c>
       <c r="G550" t="n">
-        <v>0.207896051974013</v>
+        <v>0.185407296351824</v>
       </c>
     </row>
     <row r="551">
@@ -19518,7 +19518,7 @@
         <v>1</v>
       </c>
       <c r="G551" t="n">
-        <v>0.0519740129935032</v>
+        <v>0.0604697651174413</v>
       </c>
     </row>
     <row r="552">
@@ -19583,7 +19583,7 @@
         <v>1</v>
       </c>
       <c r="G554" t="n">
-        <v>0.301849075462269</v>
+        <v>0.330334832583708</v>
       </c>
     </row>
     <row r="555">
@@ -19841,7 +19841,7 @@
         <v>1</v>
       </c>
       <c r="G566" t="n">
-        <v>0.0064967516241879</v>
+        <v>0.00699650174912544</v>
       </c>
     </row>
     <row r="567">
@@ -19864,7 +19864,7 @@
         <v>1</v>
       </c>
       <c r="G567" t="n">
-        <v>0.0749625187406297</v>
+        <v>0.0744627686156921</v>
       </c>
     </row>
     <row r="568">
@@ -19954,7 +19954,7 @@
         <v>1</v>
       </c>
       <c r="G571" t="n">
-        <v>0.310844577711144</v>
+        <v>0.311344327836082</v>
       </c>
     </row>
     <row r="572">
@@ -19977,7 +19977,7 @@
         <v>1</v>
       </c>
       <c r="G572" t="n">
-        <v>0.968515742128936</v>
+        <v>0.974012993503248</v>
       </c>
     </row>
     <row r="573">
@@ -20000,7 +20000,7 @@
         <v>1</v>
       </c>
       <c r="G573" t="n">
-        <v>0.891554222888556</v>
+        <v>0.889055472263868</v>
       </c>
     </row>
     <row r="574">
@@ -20023,7 +20023,7 @@
         <v>0</v>
       </c>
       <c r="G574" t="n">
-        <v>0.0349825087456272</v>
+        <v>0.0374812593703148</v>
       </c>
     </row>
     <row r="575">
@@ -20088,7 +20088,7 @@
         <v>1</v>
       </c>
       <c r="G577" t="n">
-        <v>0.496751624187906</v>
+        <v>0.477261369315342</v>
       </c>
     </row>
     <row r="578">
@@ -20153,7 +20153,7 @@
         <v>1</v>
       </c>
       <c r="G580" t="n">
-        <v>0.107946026986507</v>
+        <v>0.120439780109945</v>
       </c>
     </row>
     <row r="581">
@@ -20344,7 +20344,7 @@
         <v>1</v>
       </c>
       <c r="G589" t="n">
-        <v>0.746126936531734</v>
+        <v>0.737131434282859</v>
       </c>
     </row>
     <row r="590">
@@ -20430,7 +20430,7 @@
         <v>1</v>
       </c>
       <c r="G593" t="n">
-        <v>0.000499750124937531</v>
+        <v>0.000999500249875062</v>
       </c>
     </row>
     <row r="594">
@@ -20453,7 +20453,7 @@
         <v>1</v>
       </c>
       <c r="G594" t="n">
-        <v>0.169415292353823</v>
+        <v>0.162418790604698</v>
       </c>
     </row>
     <row r="595">
@@ -20476,7 +20476,7 @@
         <v>1</v>
       </c>
       <c r="G595" t="n">
-        <v>0.59720139930035</v>
+        <v>0.618190904547726</v>
       </c>
     </row>
     <row r="596">
@@ -20520,7 +20520,7 @@
         <v>1</v>
       </c>
       <c r="G597" t="n">
-        <v>0.618190904547726</v>
+        <v>0.609195402298851</v>
       </c>
     </row>
     <row r="598">
@@ -20564,7 +20564,7 @@
         <v>1</v>
       </c>
       <c r="G599" t="n">
-        <v>0.822088955522239</v>
+        <v>0.84207896051974</v>
       </c>
     </row>
     <row r="600">
@@ -20782,7 +20782,7 @@
         <v>1</v>
       </c>
       <c r="G609" t="n">
-        <v>0.48775612193903</v>
+        <v>0.492253873063468</v>
       </c>
     </row>
     <row r="610">
@@ -20870,7 +20870,7 @@
         <v>1</v>
       </c>
       <c r="G613" t="n">
-        <v>0.472263868065967</v>
+        <v>0.482758620689655</v>
       </c>
     </row>
     <row r="614">
@@ -20935,7 +20935,7 @@
         <v>1</v>
       </c>
       <c r="G616" t="n">
-        <v>0.0254872563718141</v>
+        <v>0.0424787606196902</v>
       </c>
     </row>
     <row r="617">
@@ -21023,7 +21023,7 @@
         <v>1</v>
       </c>
       <c r="G620" t="n">
-        <v>0.0594702648675662</v>
+        <v>0.0514742628685657</v>
       </c>
     </row>
     <row r="621">
@@ -21067,7 +21067,7 @@
         <v>1</v>
       </c>
       <c r="G622" t="n">
-        <v>0.192903548225887</v>
+        <v>0.180409795102449</v>
       </c>
     </row>
     <row r="623">
@@ -21237,7 +21237,7 @@
         <v>0</v>
       </c>
       <c r="G630" t="n">
-        <v>0.00849575212393803</v>
+        <v>0.00899550224887556</v>
       </c>
     </row>
     <row r="631">
@@ -21325,7 +21325,7 @@
         <v>1</v>
       </c>
       <c r="G634" t="n">
-        <v>0.0204897551224388</v>
+        <v>0.0239880059970015</v>
       </c>
     </row>
     <row r="635">
@@ -21474,7 +21474,7 @@
         <v>1</v>
       </c>
       <c r="G641" t="n">
-        <v>0.547226386806597</v>
+        <v>0.52623688155922</v>
       </c>
     </row>
     <row r="642">
@@ -21497,7 +21497,7 @@
         <v>1</v>
       </c>
       <c r="G642" t="n">
-        <v>0.161419290354823</v>
+        <v>0.156921539230385</v>
       </c>
     </row>
     <row r="643">
@@ -21583,7 +21583,7 @@
         <v>1</v>
       </c>
       <c r="G646" t="n">
-        <v>0.612193903048476</v>
+        <v>0.609195402298851</v>
       </c>
     </row>
     <row r="647">
@@ -21606,7 +21606,7 @@
         <v>1</v>
       </c>
       <c r="G647" t="n">
-        <v>0.0294852573713143</v>
+        <v>0.0314842578710645</v>
       </c>
     </row>
     <row r="648">
@@ -21692,7 +21692,7 @@
         <v>1</v>
       </c>
       <c r="G651" t="n">
-        <v>0.0534732633683158</v>
+        <v>0.0484757621189405</v>
       </c>
     </row>
     <row r="652">
@@ -21715,7 +21715,7 @@
         <v>1</v>
       </c>
       <c r="G652" t="n">
-        <v>0.624687656171914</v>
+        <v>0.608695652173913</v>
       </c>
     </row>
     <row r="653">
@@ -21780,7 +21780,7 @@
         <v>1</v>
       </c>
       <c r="G655" t="n">
-        <v>0.0279860069965017</v>
+        <v>0.0259870064967516</v>
       </c>
     </row>
     <row r="656">
@@ -21824,7 +21824,7 @@
         <v>1</v>
       </c>
       <c r="G657" t="n">
-        <v>0.00399800099950025</v>
+        <v>0.00599700149925037</v>
       </c>
     </row>
     <row r="658">
@@ -21847,7 +21847,7 @@
         <v>1</v>
       </c>
       <c r="G658" t="n">
-        <v>0.6031984007996</v>
+        <v>0.602198900549725</v>
       </c>
     </row>
     <row r="659">
@@ -22038,7 +22038,7 @@
         <v>1</v>
       </c>
       <c r="G667" t="n">
-        <v>0.411794102948526</v>
+        <v>0.416291854072964</v>
       </c>
     </row>
     <row r="668">
@@ -22103,7 +22103,7 @@
         <v>1</v>
       </c>
       <c r="G670" t="n">
-        <v>0.0424787606196902</v>
+        <v>0.0499750124937531</v>
       </c>
     </row>
     <row r="671">
@@ -22235,7 +22235,7 @@
         <v>1</v>
       </c>
       <c r="G676" t="n">
-        <v>0.00149925037481259</v>
+        <v>0.000499750124937531</v>
       </c>
     </row>
     <row r="677">
@@ -22279,7 +22279,7 @@
         <v>1</v>
       </c>
       <c r="G678" t="n">
-        <v>0.182908545727136</v>
+        <v>0.166416791604198</v>
       </c>
     </row>
     <row r="679">
@@ -22302,7 +22302,7 @@
         <v>1</v>
       </c>
       <c r="G679" t="n">
-        <v>0.0509745127436282</v>
+        <v>0.0544727636181909</v>
       </c>
     </row>
     <row r="680">
@@ -22430,7 +22430,7 @@
         <v>1</v>
       </c>
       <c r="G685" t="n">
-        <v>0.11344327836082</v>
+        <v>0.109445277361319</v>
       </c>
     </row>
     <row r="686">
@@ -22667,7 +22667,7 @@
         <v>1</v>
       </c>
       <c r="G696" t="n">
-        <v>0.301849075462269</v>
+        <v>0.327336331834083</v>
       </c>
     </row>
     <row r="697">
@@ -22929,7 +22929,7 @@
         <v>0</v>
       </c>
       <c r="G708" t="n">
-        <v>0.0379810094952524</v>
+        <v>0.0464767616191904</v>
       </c>
     </row>
     <row r="709">
@@ -22952,7 +22952,7 @@
         <v>1</v>
       </c>
       <c r="G709" t="n">
-        <v>0.0169915042478761</v>
+        <v>0.0144927536231884</v>
       </c>
     </row>
     <row r="710">
@@ -23038,7 +23038,7 @@
         <v>1</v>
       </c>
       <c r="G713" t="n">
-        <v>0.657671164417791</v>
+        <v>0.685657171414293</v>
       </c>
     </row>
     <row r="714">
@@ -23168,7 +23168,7 @@
         <v>1</v>
       </c>
       <c r="G719" t="n">
-        <v>0.229385307346327</v>
+        <v>0.216891554222889</v>
       </c>
     </row>
     <row r="720">
@@ -23233,7 +23233,7 @@
         <v>1</v>
       </c>
       <c r="G722" t="n">
-        <v>0.0194902548725637</v>
+        <v>0.0169915042478761</v>
       </c>
     </row>
     <row r="723">
@@ -23279,7 +23279,7 @@
         <v>1</v>
       </c>
       <c r="G724" t="n">
-        <v>0.00399800099950025</v>
+        <v>0.00749625187406297</v>
       </c>
     </row>
     <row r="725">
@@ -23344,7 +23344,7 @@
         <v>1</v>
       </c>
       <c r="G727" t="n">
-        <v>0.139930034982509</v>
+        <v>0.151424287856072</v>
       </c>
     </row>
     <row r="728">
@@ -23388,7 +23388,7 @@
         <v>1</v>
       </c>
       <c r="G729" t="n">
-        <v>0.000499750124937531</v>
+        <v>0.000999500249875062</v>
       </c>
     </row>
     <row r="730">
@@ -23453,7 +23453,7 @@
         <v>1</v>
       </c>
       <c r="G732" t="n">
-        <v>0.704147926036982</v>
+        <v>0.736131934032983</v>
       </c>
     </row>
     <row r="733">
@@ -23497,7 +23497,7 @@
         <v>1</v>
       </c>
       <c r="G734" t="n">
-        <v>0.581709145427286</v>
+        <v>0.6071964017991</v>
       </c>
     </row>
     <row r="735">
@@ -23520,7 +23520,7 @@
         <v>1</v>
       </c>
       <c r="G735" t="n">
-        <v>0.0634682658670665</v>
+        <v>0.0659670164917541</v>
       </c>
     </row>
     <row r="736">
@@ -23543,7 +23543,7 @@
         <v>1</v>
       </c>
       <c r="G736" t="n">
-        <v>0.60119940029985</v>
+        <v>0.608195902048976</v>
       </c>
     </row>
     <row r="737">
@@ -23608,7 +23608,7 @@
         <v>1</v>
       </c>
       <c r="G739" t="n">
-        <v>0.0419790104947526</v>
+        <v>0.0519740129935032</v>
       </c>
     </row>
     <row r="740">
@@ -23719,7 +23719,7 @@
         <v>1</v>
       </c>
       <c r="G744" t="n">
-        <v>0.000999500249875062</v>
+        <v>0.000499750124937531</v>
       </c>
     </row>
     <row r="745">
@@ -23742,7 +23742,7 @@
         <v>1</v>
       </c>
       <c r="G745" t="n">
-        <v>0.0269865067466267</v>
+        <v>0.0219890054972514</v>
       </c>
     </row>
     <row r="746">
@@ -23765,7 +23765,7 @@
         <v>1</v>
       </c>
       <c r="G746" t="n">
-        <v>0.480759620189905</v>
+        <v>0.480259870064968</v>
       </c>
     </row>
     <row r="747">
@@ -23832,7 +23832,7 @@
         <v>1</v>
       </c>
       <c r="G749" t="n">
-        <v>0.599700149925038</v>
+        <v>0.604197901049475</v>
       </c>
     </row>
     <row r="750">
@@ -23876,7 +23876,7 @@
         <v>1</v>
       </c>
       <c r="G751" t="n">
-        <v>0.000499750124937531</v>
+        <v>0.000999500249875062</v>
       </c>
     </row>
     <row r="752">
@@ -23899,7 +23899,7 @@
         <v>1</v>
       </c>
       <c r="G752" t="n">
-        <v>0.316341829085457</v>
+        <v>0.298850574712644</v>
       </c>
     </row>
     <row r="753">
@@ -23966,7 +23966,7 @@
         <v>1</v>
       </c>
       <c r="G755" t="n">
-        <v>0.237381309345327</v>
+        <v>0.253373313343328</v>
       </c>
     </row>
     <row r="756">
@@ -24031,7 +24031,7 @@
         <v>0</v>
       </c>
       <c r="G758" t="n">
-        <v>0.000499750124937531</v>
+        <v>0.000999500249875062</v>
       </c>
     </row>
     <row r="759">
@@ -24054,7 +24054,7 @@
         <v>1</v>
       </c>
       <c r="G759" t="n">
-        <v>0.228885557221389</v>
+        <v>0.234382808595702</v>
       </c>
     </row>
     <row r="760">
@@ -24140,7 +24140,7 @@
         <v>1</v>
       </c>
       <c r="G763" t="n">
-        <v>0.894052973513243</v>
+        <v>0.898550724637681</v>
       </c>
     </row>
     <row r="764">
@@ -24205,7 +24205,7 @@
         <v>0</v>
       </c>
       <c r="G766" t="n">
-        <v>0.0299850074962519</v>
+        <v>0.0339830084957521</v>
       </c>
     </row>
     <row r="767">
@@ -24314,7 +24314,7 @@
         <v>1</v>
       </c>
       <c r="G771" t="n">
-        <v>0.616691654172913</v>
+        <v>0.589205397301349</v>
       </c>
     </row>
     <row r="772">
@@ -24337,7 +24337,7 @@
         <v>1</v>
       </c>
       <c r="G772" t="n">
-        <v>0.36231884057971</v>
+        <v>0.379810094952524</v>
       </c>
     </row>
     <row r="773">
@@ -24429,7 +24429,7 @@
         <v>0</v>
       </c>
       <c r="G776" t="n">
-        <v>0.0134932533733133</v>
+        <v>0.0109945027486257</v>
       </c>
     </row>
     <row r="777">
@@ -24517,7 +24517,7 @@
         <v>1</v>
       </c>
       <c r="G780" t="n">
-        <v>0.0104947526236882</v>
+        <v>0.0134932533733133</v>
       </c>
     </row>
     <row r="781">
@@ -24668,7 +24668,7 @@
         <v>1</v>
       </c>
       <c r="G787" t="n">
-        <v>0.231884057971014</v>
+        <v>0.24287856071964</v>
       </c>
     </row>
     <row r="788">
@@ -24691,7 +24691,7 @@
         <v>1</v>
       </c>
       <c r="G788" t="n">
-        <v>0.0474762618690655</v>
+        <v>0.0514742628685657</v>
       </c>
     </row>
     <row r="789">
@@ -24714,7 +24714,7 @@
         <v>1</v>
       </c>
       <c r="G789" t="n">
-        <v>0.254872563718141</v>
+        <v>0.243878060969515</v>
       </c>
     </row>
     <row r="790">
@@ -24758,7 +24758,7 @@
         <v>0</v>
       </c>
       <c r="G791" t="n">
-        <v>0.000999500249875062</v>
+        <v>0.000499750124937531</v>
       </c>
     </row>
     <row r="792">
@@ -24888,7 +24888,7 @@
         <v>1</v>
       </c>
       <c r="G797" t="n">
-        <v>0.28535732133933</v>
+        <v>0.290354822588706</v>
       </c>
     </row>
     <row r="798">
@@ -25060,7 +25060,7 @@
         <v>1</v>
       </c>
       <c r="G805" t="n">
-        <v>0.0119940029985007</v>
+        <v>0.00999500249875063</v>
       </c>
     </row>
     <row r="806">
@@ -25083,7 +25083,7 @@
         <v>1</v>
       </c>
       <c r="G806" t="n">
-        <v>0.233383308345827</v>
+        <v>0.237381309345327</v>
       </c>
     </row>
     <row r="807">
@@ -25171,7 +25171,7 @@
         <v>1</v>
       </c>
       <c r="G810" t="n">
-        <v>0.0179910044977511</v>
+        <v>0.0139930034982509</v>
       </c>
     </row>
     <row r="811">
@@ -25347,7 +25347,7 @@
         <v>1</v>
       </c>
       <c r="G818" t="n">
-        <v>0.0984507746126937</v>
+        <v>0.107446276861569</v>
       </c>
     </row>
     <row r="819">
@@ -25565,7 +25565,7 @@
         <v>1</v>
       </c>
       <c r="G828" t="n">
-        <v>0.0424787606196902</v>
+        <v>0.0494752623688156</v>
       </c>
     </row>
     <row r="829">
@@ -25735,7 +25735,7 @@
         <v>1</v>
       </c>
       <c r="G836" t="n">
-        <v>0.0544727636181909</v>
+        <v>0.0434782608695652</v>
       </c>
     </row>
     <row r="837">
@@ -25823,7 +25823,7 @@
         <v>1</v>
       </c>
       <c r="G840" t="n">
-        <v>0.0134932533733133</v>
+        <v>0.00899550224887556</v>
       </c>
     </row>
     <row r="841">
@@ -25846,7 +25846,7 @@
         <v>1</v>
       </c>
       <c r="G841" t="n">
-        <v>0.0629685157421289</v>
+        <v>0.0759620189905048</v>
       </c>
     </row>
     <row r="842">
@@ -25869,7 +25869,7 @@
         <v>1</v>
       </c>
       <c r="G842" t="n">
-        <v>0.145427286356822</v>
+        <v>0.145927036481759</v>
       </c>
     </row>
     <row r="843">
@@ -25892,7 +25892,7 @@
         <v>1</v>
       </c>
       <c r="G843" t="n">
-        <v>0.249375312343828</v>
+        <v>0.230884557721139</v>
       </c>
     </row>
     <row r="844">
@@ -25980,7 +25980,7 @@
         <v>0</v>
       </c>
       <c r="G847" t="n">
-        <v>0.00399800099950025</v>
+        <v>0.00199900049975012</v>
       </c>
     </row>
     <row r="848">
@@ -26089,7 +26089,7 @@
         <v>1</v>
       </c>
       <c r="G852" t="n">
-        <v>0.261369315342329</v>
+        <v>0.289355322338831</v>
       </c>
     </row>
     <row r="853">
@@ -26112,7 +26112,7 @@
         <v>1</v>
       </c>
       <c r="G853" t="n">
-        <v>0.865067466266867</v>
+        <v>0.868065967016492</v>
       </c>
     </row>
     <row r="854">
@@ -26135,7 +26135,7 @@
         <v>1</v>
       </c>
       <c r="G854" t="n">
-        <v>0.0174912543728136</v>
+        <v>0.0079960019990005</v>
       </c>
     </row>
     <row r="855">
@@ -26179,7 +26179,7 @@
         <v>1</v>
       </c>
       <c r="G856" t="n">
-        <v>0.0279860069965017</v>
+        <v>0.0269865067466267</v>
       </c>
     </row>
     <row r="857">
@@ -26269,7 +26269,7 @@
         <v>1</v>
       </c>
       <c r="G860" t="n">
-        <v>0.0194902548725637</v>
+        <v>0.0164917541229385</v>
       </c>
     </row>
     <row r="861">
@@ -26313,7 +26313,7 @@
         <v>1</v>
       </c>
       <c r="G862" t="n">
-        <v>0.730634682658671</v>
+        <v>0.745127436281859</v>
       </c>
     </row>
     <row r="863">
@@ -26336,7 +26336,7 @@
         <v>1</v>
       </c>
       <c r="G863" t="n">
-        <v>0.489255372313843</v>
+        <v>0.488255872063968</v>
       </c>
     </row>
     <row r="864">
@@ -26443,7 +26443,7 @@
         <v>1</v>
       </c>
       <c r="G868" t="n">
-        <v>0.0609695152423788</v>
+        <v>0.0704647676161919</v>
       </c>
     </row>
     <row r="869">
@@ -26508,7 +26508,7 @@
         <v>1</v>
       </c>
       <c r="G871" t="n">
-        <v>0.00699650174912544</v>
+        <v>0.0079960019990005</v>
       </c>
     </row>
     <row r="872">
@@ -26531,7 +26531,7 @@
         <v>1</v>
       </c>
       <c r="G872" t="n">
-        <v>0.0414792603698151</v>
+        <v>0.0514742628685657</v>
       </c>
     </row>
     <row r="873">
@@ -26575,7 +26575,7 @@
         <v>1</v>
       </c>
       <c r="G874" t="n">
-        <v>0.0179910044977511</v>
+        <v>0.0119940029985007</v>
       </c>
     </row>
     <row r="875">
@@ -26619,7 +26619,7 @@
         <v>1</v>
       </c>
       <c r="G876" t="n">
-        <v>0.177911044477761</v>
+        <v>0.139430284857571</v>
       </c>
     </row>
     <row r="877">
@@ -26642,7 +26642,7 @@
         <v>1</v>
       </c>
       <c r="G877" t="n">
-        <v>0.128435782108946</v>
+        <v>0.124937531234383</v>
       </c>
     </row>
     <row r="878">
@@ -26665,7 +26665,7 @@
         <v>0</v>
       </c>
       <c r="G878" t="n">
-        <v>0.0124937531234383</v>
+        <v>0.0119940029985007</v>
       </c>
     </row>
     <row r="879">
@@ -26751,7 +26751,7 @@
         <v>1</v>
       </c>
       <c r="G882" t="n">
-        <v>0.0469765117441279</v>
+        <v>0.0449775112443778</v>
       </c>
     </row>
     <row r="883">
@@ -26774,7 +26774,7 @@
         <v>1</v>
       </c>
       <c r="G883" t="n">
-        <v>0.56471764117941</v>
+        <v>0.56071964017991</v>
       </c>
     </row>
     <row r="884">
@@ -26797,7 +26797,7 @@
         <v>1</v>
       </c>
       <c r="G884" t="n">
-        <v>0.249375312343828</v>
+        <v>0.256871564217891</v>
       </c>
     </row>
     <row r="885">
@@ -26820,7 +26820,7 @@
         <v>1</v>
       </c>
       <c r="G885" t="n">
-        <v>0.63568215892054</v>
+        <v>0.608695652173913</v>
       </c>
     </row>
     <row r="886">
@@ -26950,7 +26950,7 @@
         <v>1</v>
       </c>
       <c r="G891" t="n">
-        <v>0.606696651674163</v>
+        <v>0.590204897551224</v>
       </c>
     </row>
     <row r="892">
@@ -27057,7 +27057,7 @@
         <v>1</v>
       </c>
       <c r="G896" t="n">
-        <v>0.00199900049975012</v>
+        <v>0.00399800099950025</v>
       </c>
     </row>
     <row r="897">
@@ -27147,7 +27147,7 @@
         <v>0</v>
       </c>
       <c r="G900" t="n">
-        <v>0.00149925037481259</v>
+        <v>0.000999500249875062</v>
       </c>
     </row>
     <row r="901">
@@ -27382,7 +27382,7 @@
         <v>1</v>
       </c>
       <c r="G911" t="n">
-        <v>0.288855572213893</v>
+        <v>0.285857071464268</v>
       </c>
     </row>
     <row r="912">
@@ -27426,7 +27426,7 @@
         <v>1</v>
       </c>
       <c r="G913" t="n">
-        <v>0.000499750124937531</v>
+        <v>0.000999500249875062</v>
       </c>
     </row>
     <row r="914">
@@ -27579,7 +27579,7 @@
         <v>1</v>
       </c>
       <c r="G920" t="n">
-        <v>0.738630684657671</v>
+        <v>0.740629685157421</v>
       </c>
     </row>
     <row r="921">
@@ -27623,7 +27623,7 @@
         <v>1</v>
       </c>
       <c r="G922" t="n">
-        <v>0.024487756121939</v>
+        <v>0.0224887556221889</v>
       </c>
     </row>
     <row r="923">
@@ -27646,7 +27646,7 @@
         <v>1</v>
       </c>
       <c r="G923" t="n">
-        <v>0.0444777611194403</v>
+        <v>0.0469765117441279</v>
       </c>
     </row>
     <row r="924">
@@ -27669,7 +27669,7 @@
         <v>1</v>
       </c>
       <c r="G924" t="n">
-        <v>0.436281859070465</v>
+        <v>0.44527736131934</v>
       </c>
     </row>
     <row r="925">
@@ -27713,7 +27713,7 @@
         <v>1</v>
       </c>
       <c r="G926" t="n">
-        <v>0.0154922538730635</v>
+        <v>0.0169915042478761</v>
       </c>
     </row>
     <row r="927">
@@ -27757,7 +27757,7 @@
         <v>1</v>
       </c>
       <c r="G928" t="n">
-        <v>0.325337331334333</v>
+        <v>0.31584207896052</v>
       </c>
     </row>
     <row r="929">
@@ -27780,7 +27780,7 @@
         <v>1</v>
       </c>
       <c r="G929" t="n">
-        <v>0.00599700149925037</v>
+        <v>0.0064967516241879</v>
       </c>
     </row>
     <row r="930">
@@ -27824,7 +27824,7 @@
         <v>1</v>
       </c>
       <c r="G931" t="n">
-        <v>0.384807596201899</v>
+        <v>0.372313843078461</v>
       </c>
     </row>
     <row r="932">
@@ -27847,7 +27847,7 @@
         <v>1</v>
       </c>
       <c r="G932" t="n">
-        <v>0.0454772613693153</v>
+        <v>0.0434782608695652</v>
       </c>
     </row>
     <row r="933">
@@ -27893,7 +27893,7 @@
         <v>1</v>
       </c>
       <c r="G934" t="n">
-        <v>0.183908045977011</v>
+        <v>0.172913543228386</v>
       </c>
     </row>
     <row r="935">
@@ -27958,7 +27958,7 @@
         <v>1</v>
       </c>
       <c r="G937" t="n">
-        <v>0.5952023988006</v>
+        <v>0.603698150924538</v>
       </c>
     </row>
     <row r="938">
@@ -27981,7 +27981,7 @@
         <v>1</v>
       </c>
       <c r="G938" t="n">
-        <v>0.857571214392804</v>
+        <v>0.864067966016992</v>
       </c>
     </row>
     <row r="939">
@@ -28088,7 +28088,7 @@
         <v>1</v>
       </c>
       <c r="G943" t="n">
-        <v>0.738630684657671</v>
+        <v>0.741129435282359</v>
       </c>
     </row>
     <row r="944">
@@ -28321,7 +28321,7 @@
         <v>0</v>
       </c>
       <c r="G954" t="n">
-        <v>0.0624687656171914</v>
+        <v>0.0569715142428786</v>
       </c>
     </row>
     <row r="955">
@@ -28344,7 +28344,7 @@
         <v>1</v>
       </c>
       <c r="G955" t="n">
-        <v>0.197401299350325</v>
+        <v>0.183908045977011</v>
       </c>
     </row>
     <row r="956">
@@ -28430,7 +28430,7 @@
         <v>1</v>
       </c>
       <c r="G959" t="n">
-        <v>0.243378310844578</v>
+        <v>0.223888055972014</v>
       </c>
     </row>
     <row r="960">
@@ -28453,7 +28453,7 @@
         <v>1</v>
       </c>
       <c r="G960" t="n">
-        <v>0.141929035482259</v>
+        <v>0.137431284357821</v>
       </c>
     </row>
     <row r="961">
@@ -28476,7 +28476,7 @@
         <v>1</v>
       </c>
       <c r="G961" t="n">
-        <v>0.00249875062468766</v>
+        <v>0.00599700149925037</v>
       </c>
     </row>
     <row r="962">
@@ -28520,7 +28520,7 @@
         <v>1</v>
       </c>
       <c r="G963" t="n">
-        <v>0.0179910044977511</v>
+        <v>0.0204897551224388</v>
       </c>
     </row>
     <row r="964">
@@ -28543,7 +28543,7 @@
         <v>1</v>
       </c>
       <c r="G964" t="n">
-        <v>0.153423288355822</v>
+        <v>0.166416791604198</v>
       </c>
     </row>
     <row r="965">
@@ -28587,7 +28587,7 @@
         <v>0</v>
       </c>
       <c r="G966" t="n">
-        <v>0.00349825087456272</v>
+        <v>0.00749625187406297</v>
       </c>
     </row>
     <row r="967">
@@ -28717,7 +28717,7 @@
         <v>0</v>
       </c>
       <c r="G972" t="n">
-        <v>0.00549725137431284</v>
+        <v>0.00449775112443778</v>
       </c>
     </row>
     <row r="973">
@@ -28740,7 +28740,7 @@
         <v>1</v>
       </c>
       <c r="G973" t="n">
-        <v>0.48375812093953</v>
+        <v>0.488755622188906</v>
       </c>
     </row>
     <row r="974">
@@ -28805,7 +28805,7 @@
         <v>1</v>
       </c>
       <c r="G976" t="n">
-        <v>0.236381809095452</v>
+        <v>0.24487756121939</v>
       </c>
     </row>
     <row r="977">
@@ -28870,7 +28870,7 @@
         <v>1</v>
       </c>
       <c r="G979" t="n">
-        <v>0.0114942528735632</v>
+        <v>0.00949525237381309</v>
       </c>
     </row>
     <row r="980">
@@ -28935,7 +28935,7 @@
         <v>1</v>
       </c>
       <c r="G982" t="n">
-        <v>0.153423288355822</v>
+        <v>0.152423788105947</v>
       </c>
     </row>
     <row r="983">
@@ -28958,7 +28958,7 @@
         <v>1</v>
       </c>
       <c r="G983" t="n">
-        <v>0.0294852573713143</v>
+        <v>0.0414792603698151</v>
       </c>
     </row>
     <row r="984">
@@ -29025,7 +29025,7 @@
         <v>0</v>
       </c>
       <c r="G986" t="n">
-        <v>0.0184907546226887</v>
+        <v>0.0174912543728136</v>
       </c>
     </row>
     <row r="987">
@@ -29048,7 +29048,7 @@
         <v>1</v>
       </c>
       <c r="G987" t="n">
-        <v>0.842578710644678</v>
+        <v>0.84007996001999</v>
       </c>
     </row>
     <row r="988">
@@ -29392,7 +29392,7 @@
         <v>1</v>
       </c>
       <c r="G1003" t="n">
-        <v>0.611694152923538</v>
+        <v>0.5992003998001</v>
       </c>
     </row>
     <row r="1004">
@@ -29627,7 +29627,7 @@
         <v>1</v>
       </c>
       <c r="G1014" t="n">
-        <v>0.594702648675662</v>
+        <v>0.590704647676162</v>
       </c>
     </row>
     <row r="1015">
@@ -29671,7 +29671,7 @@
         <v>1</v>
       </c>
       <c r="G1016" t="n">
-        <v>0.837581209395302</v>
+        <v>0.837081459270365</v>
       </c>
     </row>
     <row r="1017">
@@ -29736,7 +29736,7 @@
         <v>0</v>
       </c>
       <c r="G1019" t="n">
-        <v>0.00999500249875063</v>
+        <v>0.0134932533733133</v>
       </c>
     </row>
     <row r="1020">
@@ -29780,7 +29780,7 @@
         <v>1</v>
       </c>
       <c r="G1021" t="n">
-        <v>0.0469765117441279</v>
+        <v>0.0429785107446277</v>
       </c>
     </row>
     <row r="1022">
@@ -29870,7 +29870,7 @@
         <v>1</v>
       </c>
       <c r="G1025" t="n">
-        <v>0.625687156421789</v>
+        <v>0.60119940029985</v>
       </c>
     </row>
     <row r="1026">
@@ -29893,7 +29893,7 @@
         <v>1</v>
       </c>
       <c r="G1026" t="n">
-        <v>0.606696651674163</v>
+        <v>0.589205397301349</v>
       </c>
     </row>
     <row r="1027">
@@ -30151,7 +30151,7 @@
         <v>1</v>
       </c>
       <c r="G1038" t="n">
-        <v>0.466766616691654</v>
+        <v>0.474762618690655</v>
       </c>
     </row>
     <row r="1039">
@@ -30195,7 +30195,7 @@
         <v>0</v>
       </c>
       <c r="G1040" t="n">
-        <v>0.00999500249875063</v>
+        <v>0.0124937531234383</v>
       </c>
     </row>
     <row r="1041">
@@ -30348,7 +30348,7 @@
         <v>1</v>
       </c>
       <c r="G1047" t="n">
-        <v>0.00599700149925037</v>
+        <v>0.00699650174912544</v>
       </c>
     </row>
     <row r="1048">
@@ -30438,7 +30438,7 @@
         <v>1</v>
       </c>
       <c r="G1051" t="n">
-        <v>0.501249375312344</v>
+        <v>0.494252873563218</v>
       </c>
     </row>
     <row r="1052">
@@ -30461,7 +30461,7 @@
         <v>1</v>
       </c>
       <c r="G1052" t="n">
-        <v>0.0559720139930035</v>
+        <v>0.056471764117941</v>
       </c>
     </row>
     <row r="1053">
@@ -30591,7 +30591,7 @@
         <v>1</v>
       </c>
       <c r="G1058" t="n">
-        <v>0.609195402298851</v>
+        <v>0.599700149925038</v>
       </c>
     </row>
     <row r="1059">
@@ -30635,7 +30635,7 @@
         <v>1</v>
       </c>
       <c r="G1060" t="n">
-        <v>0.475262368815592</v>
+        <v>0.492253873063468</v>
       </c>
     </row>
     <row r="1061">
@@ -30658,7 +30658,7 @@
         <v>0</v>
       </c>
       <c r="G1061" t="n">
-        <v>0.0154922538730635</v>
+        <v>0.0179910044977511</v>
       </c>
     </row>
     <row r="1062">
@@ -30916,7 +30916,7 @@
         <v>1</v>
       </c>
       <c r="G1073" t="n">
-        <v>0.222888555722139</v>
+        <v>0.23888055972014</v>
       </c>
     </row>
     <row r="1074">
@@ -30939,7 +30939,7 @@
         <v>1</v>
       </c>
       <c r="G1074" t="n">
-        <v>0.243378310844578</v>
+        <v>0.230384807596202</v>
       </c>
     </row>
     <row r="1075">
@@ -31067,7 +31067,7 @@
         <v>1</v>
       </c>
       <c r="G1080" t="n">
-        <v>0.00249875062468766</v>
+        <v>0.00149925037481259</v>
       </c>
     </row>
     <row r="1081">
@@ -31090,7 +31090,7 @@
         <v>0</v>
       </c>
       <c r="G1081" t="n">
-        <v>0.0299850074962519</v>
+        <v>0.0259870064967516</v>
       </c>
     </row>
     <row r="1082">
@@ -31157,7 +31157,7 @@
         <v>1</v>
       </c>
       <c r="G1084" t="n">
-        <v>0.0124937531234383</v>
+        <v>0.0144927536231884</v>
       </c>
     </row>
     <row r="1085">
@@ -31224,7 +31224,7 @@
         <v>1</v>
       </c>
       <c r="G1087" t="n">
-        <v>0.158420789605197</v>
+        <v>0.156421789105447</v>
       </c>
     </row>
     <row r="1088">
@@ -31247,7 +31247,7 @@
         <v>1</v>
       </c>
       <c r="G1088" t="n">
-        <v>0.513243378310845</v>
+        <v>0.498250874562719</v>
       </c>
     </row>
     <row r="1089">
@@ -31377,7 +31377,7 @@
         <v>1</v>
       </c>
       <c r="G1094" t="n">
-        <v>0.189405297351324</v>
+        <v>0.197901049475262</v>
       </c>
     </row>
     <row r="1095">
@@ -31486,7 +31486,7 @@
         <v>1</v>
       </c>
       <c r="G1099" t="n">
-        <v>0.0484757621189405</v>
+        <v>0.0534732633683158</v>
       </c>
     </row>
     <row r="1100">
@@ -31721,7 +31721,7 @@
         <v>1</v>
       </c>
       <c r="G1110" t="n">
-        <v>0.95552223888056</v>
+        <v>0.956521739130435</v>
       </c>
     </row>
     <row r="1111">
@@ -31744,7 +31744,7 @@
         <v>1</v>
       </c>
       <c r="G1111" t="n">
-        <v>0.0759620189905048</v>
+        <v>0.0699650174912544</v>
       </c>
     </row>
     <row r="1112">
@@ -31809,7 +31809,7 @@
         <v>1</v>
       </c>
       <c r="G1114" t="n">
-        <v>0.00699650174912544</v>
+        <v>0.00549725137431284</v>
       </c>
     </row>
     <row r="1115">
@@ -31853,7 +31853,7 @@
         <v>1</v>
       </c>
       <c r="G1116" t="n">
-        <v>0.0699650174912544</v>
+        <v>0.0589705147426287</v>
       </c>
     </row>
     <row r="1117">
@@ -31899,7 +31899,7 @@
         <v>1</v>
       </c>
       <c r="G1118" t="n">
-        <v>0.309845077461269</v>
+        <v>0.31184407796102</v>
       </c>
     </row>
     <row r="1119">
@@ -31922,7 +31922,7 @@
         <v>1</v>
       </c>
       <c r="G1119" t="n">
-        <v>0.714142928535732</v>
+        <v>0.696651674162919</v>
       </c>
     </row>
     <row r="1120">
@@ -31945,7 +31945,7 @@
         <v>1</v>
       </c>
       <c r="G1120" t="n">
-        <v>0.114942528735632</v>
+        <v>0.0949525237381309</v>
       </c>
     </row>
     <row r="1121">
@@ -31968,7 +31968,7 @@
         <v>1</v>
       </c>
       <c r="G1121" t="n">
-        <v>0.000999500249875062</v>
+        <v>0.000499750124937531</v>
       </c>
     </row>
     <row r="1122">
@@ -32012,7 +32012,7 @@
         <v>1</v>
       </c>
       <c r="G1123" t="n">
-        <v>0.866066966516742</v>
+        <v>0.870064967516242</v>
       </c>
     </row>
     <row r="1124">
@@ -32058,7 +32058,7 @@
         <v>1</v>
       </c>
       <c r="G1125" t="n">
-        <v>0.00949525237381309</v>
+        <v>0.0184907546226887</v>
       </c>
     </row>
     <row r="1126">
@@ -32148,7 +32148,7 @@
         <v>1</v>
       </c>
       <c r="G1129" t="n">
-        <v>0.0429785107446277</v>
+        <v>0.0354822588705647</v>
       </c>
     </row>
     <row r="1130">
@@ -32171,7 +32171,7 @@
         <v>0</v>
       </c>
       <c r="G1130" t="n">
-        <v>0.0629685157421289</v>
+        <v>0.0719640179910045</v>
       </c>
     </row>
     <row r="1131">
@@ -32259,7 +32259,7 @@
         <v>1</v>
       </c>
       <c r="G1134" t="n">
-        <v>0.898050974512744</v>
+        <v>0.894552723638181</v>
       </c>
     </row>
     <row r="1135">
@@ -32303,7 +32303,7 @@
         <v>1</v>
       </c>
       <c r="G1136" t="n">
-        <v>0.36231884057971</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="1137">
@@ -32326,7 +32326,7 @@
         <v>1</v>
       </c>
       <c r="G1137" t="n">
-        <v>0.250874562718641</v>
+        <v>0.23488255872064</v>
       </c>
     </row>
     <row r="1138">
@@ -32393,7 +32393,7 @@
         <v>0</v>
       </c>
       <c r="G1140" t="n">
-        <v>0.00299850074962519</v>
+        <v>0.00199900049975012</v>
       </c>
     </row>
     <row r="1141">
@@ -32502,7 +32502,7 @@
         <v>1</v>
       </c>
       <c r="G1145" t="n">
-        <v>0.0334832583708146</v>
+        <v>0.031984007996002</v>
       </c>
     </row>
     <row r="1146">
@@ -32567,7 +32567,7 @@
         <v>1</v>
       </c>
       <c r="G1148" t="n">
-        <v>0.000999500249875062</v>
+        <v>0.000499750124937531</v>
       </c>
     </row>
     <row r="1149">
@@ -32611,7 +32611,7 @@
         <v>1</v>
       </c>
       <c r="G1150" t="n">
-        <v>0.00699650174912544</v>
+        <v>0.0119940029985007</v>
       </c>
     </row>
     <row r="1151">
@@ -32634,7 +32634,7 @@
         <v>1</v>
       </c>
       <c r="G1151" t="n">
-        <v>0.344327836081959</v>
+        <v>0.342828585707146</v>
       </c>
     </row>
     <row r="1152">
@@ -32701,7 +32701,7 @@
         <v>1</v>
       </c>
       <c r="G1154" t="n">
-        <v>0.0659670164917541</v>
+        <v>0.0609695152423788</v>
       </c>
     </row>
     <row r="1155">
@@ -32747,7 +32747,7 @@
         <v>1</v>
       </c>
       <c r="G1156" t="n">
-        <v>0.00849575212393803</v>
+        <v>0.00749625187406297</v>
       </c>
     </row>
     <row r="1157">
@@ -32770,7 +32770,7 @@
         <v>1</v>
       </c>
       <c r="G1157" t="n">
-        <v>0.870064967516242</v>
+        <v>0.863068465767116</v>
       </c>
     </row>
     <row r="1158">
@@ -32814,7 +32814,7 @@
         <v>1</v>
       </c>
       <c r="G1159" t="n">
-        <v>0.440779610194903</v>
+        <v>0.424287856071964</v>
       </c>
     </row>
     <row r="1160">
@@ -32860,7 +32860,7 @@
         <v>1</v>
       </c>
       <c r="G1161" t="n">
-        <v>0.251874062968516</v>
+        <v>0.230384807596202</v>
       </c>
     </row>
     <row r="1162">
@@ -32906,7 +32906,7 @@
         <v>1</v>
       </c>
       <c r="G1163" t="n">
-        <v>0.513743128435782</v>
+        <v>0.511244377811094</v>
       </c>
     </row>
     <row r="1164">
@@ -33013,7 +33013,7 @@
         <v>1</v>
       </c>
       <c r="G1168" t="n">
-        <v>0.00249875062468766</v>
+        <v>0.000999500249875062</v>
       </c>
     </row>
     <row r="1169">
@@ -33099,7 +33099,7 @@
         <v>1</v>
       </c>
       <c r="G1172" t="n">
-        <v>0.193903048475762</v>
+        <v>0.179410294852574</v>
       </c>
     </row>
     <row r="1173">
@@ -33187,7 +33187,7 @@
         <v>1</v>
       </c>
       <c r="G1176" t="n">
-        <v>0.0064967516241879</v>
+        <v>0.00499750124937531</v>
       </c>
     </row>
     <row r="1177">
@@ -33231,7 +33231,7 @@
         <v>1</v>
       </c>
       <c r="G1178" t="n">
-        <v>0.860569715142429</v>
+        <v>0.862068965517241</v>
       </c>
     </row>
     <row r="1179">
@@ -33296,7 +33296,7 @@
         <v>1</v>
       </c>
       <c r="G1181" t="n">
-        <v>0.15992003998001</v>
+        <v>0.155422288855572</v>
       </c>
     </row>
     <row r="1182">
@@ -33319,7 +33319,7 @@
         <v>1</v>
       </c>
       <c r="G1182" t="n">
-        <v>0.0114942528735632</v>
+        <v>0.0104947526236882</v>
       </c>
     </row>
     <row r="1183">
@@ -33386,7 +33386,7 @@
         <v>1</v>
       </c>
       <c r="G1185" t="n">
-        <v>0.0109945027486257</v>
+        <v>0.00749625187406297</v>
       </c>
     </row>
     <row r="1186">
@@ -33432,7 +33432,7 @@
         <v>1</v>
       </c>
       <c r="G1187" t="n">
-        <v>0.047976011994003</v>
+        <v>0.0419790104947526</v>
       </c>
     </row>
     <row r="1188">
@@ -33476,7 +33476,7 @@
         <v>1</v>
       </c>
       <c r="G1189" t="n">
-        <v>0.615192403798101</v>
+        <v>0.613193403298351</v>
       </c>
     </row>
     <row r="1190">
@@ -33541,7 +33541,7 @@
         <v>1</v>
       </c>
       <c r="G1192" t="n">
-        <v>0.395802098950525</v>
+        <v>0.385307346326837</v>
       </c>
     </row>
     <row r="1193">
@@ -33677,7 +33677,7 @@
         <v>1</v>
       </c>
       <c r="G1198" t="n">
-        <v>0.663668165917041</v>
+        <v>0.672663668165917</v>
       </c>
     </row>
     <row r="1199">
@@ -33700,7 +33700,7 @@
         <v>1</v>
       </c>
       <c r="G1199" t="n">
-        <v>0.537231384307846</v>
+        <v>0.542728635682159</v>
       </c>
     </row>
     <row r="1200">
@@ -33744,7 +33744,7 @@
         <v>1</v>
       </c>
       <c r="G1201" t="n">
-        <v>0.047976011994003</v>
+        <v>0.0424787606196902</v>
       </c>
     </row>
     <row r="1202">
@@ -33788,7 +33788,7 @@
         <v>1</v>
       </c>
       <c r="G1203" t="n">
-        <v>0.0634682658670665</v>
+        <v>0.063968015992004</v>
       </c>
     </row>
     <row r="1204">
@@ -33811,7 +33811,7 @@
         <v>1</v>
       </c>
       <c r="G1204" t="n">
-        <v>0.149425287356322</v>
+        <v>0.15392303848076</v>
       </c>
     </row>
     <row r="1205">
@@ -33857,7 +33857,7 @@
         <v>1</v>
       </c>
       <c r="G1206" t="n">
-        <v>0.237381309345327</v>
+        <v>0.24287856071964</v>
       </c>
     </row>
     <row r="1207">
@@ -33901,7 +33901,7 @@
         <v>1</v>
       </c>
       <c r="G1208" t="n">
-        <v>0.128435782108946</v>
+        <v>0.139430284857571</v>
       </c>
     </row>
     <row r="1209">
@@ -33924,7 +33924,7 @@
         <v>1</v>
       </c>
       <c r="G1209" t="n">
-        <v>0.0184907546226887</v>
+        <v>0.0179910044977511</v>
       </c>
     </row>
     <row r="1210">
@@ -33947,7 +33947,7 @@
         <v>1</v>
       </c>
       <c r="G1210" t="n">
-        <v>0.216891554222889</v>
+        <v>0.233883058470765</v>
       </c>
     </row>
     <row r="1211">
@@ -33970,7 +33970,7 @@
         <v>1</v>
       </c>
       <c r="G1211" t="n">
-        <v>0.600199900049975</v>
+        <v>0.605697151424288</v>
       </c>
     </row>
     <row r="1212">
@@ -33993,7 +33993,7 @@
         <v>1</v>
       </c>
       <c r="G1212" t="n">
-        <v>0.199400299850075</v>
+        <v>0.190904547726137</v>
       </c>
     </row>
     <row r="1213">
@@ -34016,7 +34016,7 @@
         <v>1</v>
       </c>
       <c r="G1213" t="n">
-        <v>0.417291354322839</v>
+        <v>0.419290354822589</v>
       </c>
     </row>
     <row r="1214">
@@ -34062,7 +34062,7 @@
         <v>1</v>
       </c>
       <c r="G1215" t="n">
-        <v>0.813093453273363</v>
+        <v>0.814092953523238</v>
       </c>
     </row>
     <row r="1216">
@@ -34085,7 +34085,7 @@
         <v>0</v>
       </c>
       <c r="G1216" t="n">
-        <v>0.0144927536231884</v>
+        <v>0.00999500249875063</v>
       </c>
     </row>
     <row r="1217">
@@ -34131,7 +34131,7 @@
         <v>1</v>
       </c>
       <c r="G1218" t="n">
-        <v>0.705147426286857</v>
+        <v>0.695152423788106</v>
       </c>
     </row>
     <row r="1219">
@@ -34175,7 +34175,7 @@
         <v>1</v>
       </c>
       <c r="G1220" t="n">
-        <v>0.11944027986007</v>
+        <v>0.119940029985007</v>
       </c>
     </row>
     <row r="1221">
@@ -34219,7 +34219,7 @@
         <v>1</v>
       </c>
       <c r="G1222" t="n">
-        <v>0.0374812593703148</v>
+        <v>0.0444777611194403</v>
       </c>
     </row>
     <row r="1223">
@@ -34284,7 +34284,7 @@
         <v>1</v>
       </c>
       <c r="G1225" t="n">
-        <v>0.144927536231884</v>
+        <v>0.149925037481259</v>
       </c>
     </row>
     <row r="1226">
@@ -34307,7 +34307,7 @@
         <v>1</v>
       </c>
       <c r="G1226" t="n">
-        <v>0.0129935032483758</v>
+        <v>0.0154922538730635</v>
       </c>
     </row>
     <row r="1227">
@@ -34395,7 +34395,7 @@
         <v>1</v>
       </c>
       <c r="G1230" t="n">
-        <v>0.0469765117441279</v>
+        <v>0.0519740129935032</v>
       </c>
     </row>
     <row r="1231">
@@ -34439,7 +34439,7 @@
         <v>1</v>
       </c>
       <c r="G1232" t="n">
-        <v>0.162418790604698</v>
+        <v>0.160919540229885</v>
       </c>
     </row>
     <row r="1233">
@@ -34462,7 +34462,7 @@
         <v>0</v>
       </c>
       <c r="G1233" t="n">
-        <v>0.00749625187406297</v>
+        <v>0.00899550224887556</v>
       </c>
     </row>
     <row r="1234">
@@ -34506,7 +34506,7 @@
         <v>1</v>
       </c>
       <c r="G1235" t="n">
-        <v>0.0574712643678161</v>
+        <v>0.0449775112443778</v>
       </c>
     </row>
     <row r="1236">
@@ -34550,7 +34550,7 @@
         <v>1</v>
       </c>
       <c r="G1237" t="n">
-        <v>0.000499750124937531</v>
+        <v>0.000999500249875062</v>
       </c>
     </row>
     <row r="1238">
@@ -34594,7 +34594,7 @@
         <v>1</v>
       </c>
       <c r="G1239" t="n">
-        <v>0.0279860069965017</v>
+        <v>0.0259870064967516</v>
       </c>
     </row>
     <row r="1240">
@@ -34638,7 +34638,7 @@
         <v>1</v>
       </c>
       <c r="G1241" t="n">
-        <v>0.000499750124937531</v>
+        <v>0.00199900049975012</v>
       </c>
     </row>
     <row r="1242">
@@ -34661,7 +34661,7 @@
         <v>1</v>
       </c>
       <c r="G1242" t="n">
-        <v>0.00699650174912544</v>
+        <v>0.00849575212393803</v>
       </c>
     </row>
     <row r="1243">
@@ -34684,7 +34684,7 @@
         <v>1</v>
       </c>
       <c r="G1243" t="n">
-        <v>0.283858070964518</v>
+        <v>0.272863568215892</v>
       </c>
     </row>
     <row r="1244">
@@ -34728,7 +34728,7 @@
         <v>1</v>
       </c>
       <c r="G1245" t="n">
-        <v>0.312343828085957</v>
+        <v>0.300849575212394</v>
       </c>
     </row>
     <row r="1246">
@@ -34900,7 +34900,7 @@
         <v>1</v>
       </c>
       <c r="G1253" t="n">
-        <v>0.170414792603698</v>
+        <v>0.162418790604698</v>
       </c>
     </row>
     <row r="1254">
@@ -34944,7 +34944,7 @@
         <v>1</v>
       </c>
       <c r="G1255" t="n">
-        <v>0.0304847576211894</v>
+        <v>0.031984007996002</v>
       </c>
     </row>
     <row r="1256">
@@ -34967,7 +34967,7 @@
         <v>1</v>
       </c>
       <c r="G1256" t="n">
-        <v>0.152923538230885</v>
+        <v>0.155422288855572</v>
       </c>
     </row>
     <row r="1257">
@@ -34990,7 +34990,7 @@
         <v>0</v>
       </c>
       <c r="G1257" t="n">
-        <v>0.000499750124937531</v>
+        <v>0.000999500249875062</v>
       </c>
     </row>
     <row r="1258">
@@ -35013,7 +35013,7 @@
         <v>1</v>
       </c>
       <c r="G1258" t="n">
-        <v>0.0239880059970015</v>
+        <v>0.0304847576211894</v>
       </c>
     </row>
     <row r="1259">
@@ -35082,7 +35082,7 @@
         <v>1</v>
       </c>
       <c r="G1261" t="n">
-        <v>0.614692653673163</v>
+        <v>0.613193403298351</v>
       </c>
     </row>
     <row r="1262">
@@ -35105,7 +35105,7 @@
         <v>1</v>
       </c>
       <c r="G1262" t="n">
-        <v>0.327336331834083</v>
+        <v>0.313343328335832</v>
       </c>
     </row>
     <row r="1263">
@@ -35128,7 +35128,7 @@
         <v>1</v>
       </c>
       <c r="G1263" t="n">
-        <v>0.0399800099950025</v>
+        <v>0.0494752623688156</v>
       </c>
     </row>
     <row r="1264">
@@ -35172,7 +35172,7 @@
         <v>1</v>
       </c>
       <c r="G1265" t="n">
-        <v>0.470264867566217</v>
+        <v>0.469765117441279</v>
       </c>
     </row>
     <row r="1266">
@@ -35283,7 +35283,7 @@
         <v>1</v>
       </c>
       <c r="G1270" t="n">
-        <v>0.326836581709145</v>
+        <v>0.318340829585207</v>
       </c>
     </row>
     <row r="1271">
@@ -35306,7 +35306,7 @@
         <v>1</v>
       </c>
       <c r="G1271" t="n">
-        <v>0.0444777611194403</v>
+        <v>0.0469765117441279</v>
       </c>
     </row>
     <row r="1272">
@@ -35434,7 +35434,7 @@
         <v>1</v>
       </c>
       <c r="G1277" t="n">
-        <v>0.00199900049975012</v>
+        <v>0.00299850074962519</v>
       </c>
     </row>
     <row r="1278">
@@ -35501,7 +35501,7 @@
         <v>1</v>
       </c>
       <c r="G1280" t="n">
-        <v>0.0149925037481259</v>
+        <v>0.0139930034982509</v>
       </c>
     </row>
     <row r="1281">
@@ -35568,7 +35568,7 @@
         <v>1</v>
       </c>
       <c r="G1283" t="n">
-        <v>0.16591704147926</v>
+        <v>0.15392303848076</v>
       </c>
     </row>
     <row r="1284">
@@ -35635,7 +35635,7 @@
         <v>1</v>
       </c>
       <c r="G1286" t="n">
-        <v>0.604697651174413</v>
+        <v>0.611694152923538</v>
       </c>
     </row>
     <row r="1287">
@@ -35658,7 +35658,7 @@
         <v>1</v>
       </c>
       <c r="G1287" t="n">
-        <v>0.23688155922039</v>
+        <v>0.23288355822089</v>
       </c>
     </row>
     <row r="1288">
@@ -35723,7 +35723,7 @@
         <v>1</v>
       </c>
       <c r="G1290" t="n">
-        <v>0.0169915042478761</v>
+        <v>0.0144927536231884</v>
       </c>
     </row>
     <row r="1291">
@@ -35746,7 +35746,7 @@
         <v>1</v>
       </c>
       <c r="G1291" t="n">
-        <v>0.179410294852574</v>
+        <v>0.195402298850575</v>
       </c>
     </row>
     <row r="1292">
@@ -35769,7 +35769,7 @@
         <v>1</v>
       </c>
       <c r="G1292" t="n">
-        <v>0.0064967516241879</v>
+        <v>0.00699650174912544</v>
       </c>
     </row>
     <row r="1293">
@@ -35834,7 +35834,7 @@
         <v>1</v>
       </c>
       <c r="G1295" t="n">
-        <v>0.183908045977011</v>
+        <v>0.185907046476762</v>
       </c>
     </row>
     <row r="1296">
@@ -35941,7 +35941,7 @@
         <v>1</v>
       </c>
       <c r="G1300" t="n">
-        <v>0.000999500249875062</v>
+        <v>0.000499750124937531</v>
       </c>
     </row>
     <row r="1301">
@@ -35985,7 +35985,7 @@
         <v>0</v>
       </c>
       <c r="G1302" t="n">
-        <v>0.0219890054972514</v>
+        <v>0.0229885057471264</v>
       </c>
     </row>
     <row r="1303">
@@ -36052,7 +36052,7 @@
         <v>1</v>
       </c>
       <c r="G1305" t="n">
-        <v>0.0164917541229385</v>
+        <v>0.0249875062468766</v>
       </c>
     </row>
     <row r="1306">
@@ -36138,7 +36138,7 @@
         <v>1</v>
       </c>
       <c r="G1309" t="n">
-        <v>0.189905047476262</v>
+        <v>0.188405797101449</v>
       </c>
     </row>
     <row r="1310">
@@ -36161,7 +36161,7 @@
         <v>1</v>
       </c>
       <c r="G1310" t="n">
-        <v>0.671164417791104</v>
+        <v>0.659670164917541</v>
       </c>
     </row>
     <row r="1311">
@@ -36184,7 +36184,7 @@
         <v>1</v>
       </c>
       <c r="G1311" t="n">
-        <v>0.00199900049975012</v>
+        <v>0.00249875062468766</v>
       </c>
     </row>
     <row r="1312">
@@ -36207,7 +36207,7 @@
         <v>1</v>
       </c>
       <c r="G1312" t="n">
-        <v>0.28735632183908</v>
+        <v>0.288355822088956</v>
       </c>
     </row>
     <row r="1313">
@@ -36272,7 +36272,7 @@
         <v>0</v>
       </c>
       <c r="G1315" t="n">
-        <v>0.039480259870065</v>
+        <v>0.0514742628685657</v>
       </c>
     </row>
     <row r="1316">
@@ -36295,7 +36295,7 @@
         <v>1</v>
       </c>
       <c r="G1316" t="n">
-        <v>0.182408795602199</v>
+        <v>0.193903048475762</v>
       </c>
     </row>
     <row r="1317">
@@ -36318,7 +36318,7 @@
         <v>1</v>
       </c>
       <c r="G1317" t="n">
-        <v>0.162418790604698</v>
+        <v>0.16591704147926</v>
       </c>
     </row>
     <row r="1318">
@@ -36341,7 +36341,7 @@
         <v>1</v>
       </c>
       <c r="G1318" t="n">
-        <v>0.186906546726637</v>
+        <v>0.188405797101449</v>
       </c>
     </row>
     <row r="1319">
@@ -36385,7 +36385,7 @@
         <v>1</v>
       </c>
       <c r="G1320" t="n">
-        <v>0.947026486756622</v>
+        <v>0.945027486256872</v>
       </c>
     </row>
     <row r="1321">
@@ -36408,7 +36408,7 @@
         <v>1</v>
       </c>
       <c r="G1321" t="n">
-        <v>0.174412793603198</v>
+        <v>0.160419790104948</v>
       </c>
     </row>
     <row r="1322">
@@ -36452,7 +36452,7 @@
         <v>1</v>
       </c>
       <c r="G1323" t="n">
-        <v>0.385307346326837</v>
+        <v>0.383808095952024</v>
       </c>
     </row>
     <row r="1324">
@@ -36496,7 +36496,7 @@
         <v>1</v>
       </c>
       <c r="G1325" t="n">
-        <v>0.047976011994003</v>
+        <v>0.0434782608695652</v>
       </c>
     </row>
     <row r="1326">
@@ -36584,7 +36584,7 @@
         <v>1</v>
       </c>
       <c r="G1329" t="n">
-        <v>0.0154922538730635</v>
+        <v>0.0239880059970015</v>
       </c>
     </row>
     <row r="1330">
@@ -36628,7 +36628,7 @@
         <v>1</v>
       </c>
       <c r="G1331" t="n">
-        <v>0.047976011994003</v>
+        <v>0.0569715142428786</v>
       </c>
     </row>
     <row r="1332">
@@ -36651,7 +36651,7 @@
         <v>1</v>
       </c>
       <c r="G1332" t="n">
-        <v>0.00949525237381309</v>
+        <v>0.0119940029985007</v>
       </c>
     </row>
     <row r="1333">
@@ -36697,7 +36697,7 @@
         <v>1</v>
       </c>
       <c r="G1334" t="n">
-        <v>0.0834582708645677</v>
+        <v>0.0864567716141929</v>
       </c>
     </row>
     <row r="1335">
@@ -36720,7 +36720,7 @@
         <v>0</v>
       </c>
       <c r="G1335" t="n">
-        <v>0.00199900049975012</v>
+        <v>0.00249875062468766</v>
       </c>
     </row>
     <row r="1336">
@@ -36785,7 +36785,7 @@
         <v>1</v>
       </c>
       <c r="G1338" t="n">
-        <v>0.0879560219890055</v>
+        <v>0.0944527736131934</v>
       </c>
     </row>
     <row r="1339">
@@ -36850,7 +36850,7 @@
         <v>1</v>
       </c>
       <c r="G1341" t="n">
-        <v>0.0229885057471264</v>
+        <v>0.0289855072463768</v>
       </c>
     </row>
     <row r="1342">
@@ -36873,7 +36873,7 @@
         <v>1</v>
       </c>
       <c r="G1342" t="n">
-        <v>0.254372813593203</v>
+        <v>0.243878060969515</v>
       </c>
     </row>
     <row r="1343">
@@ -36896,7 +36896,7 @@
         <v>1</v>
       </c>
       <c r="G1343" t="n">
-        <v>0.00399800099950025</v>
+        <v>0.00549725137431284</v>
       </c>
     </row>
     <row r="1344">
@@ -36919,7 +36919,7 @@
         <v>1</v>
       </c>
       <c r="G1344" t="n">
-        <v>0.12743628185907</v>
+        <v>0.127936031984008</v>
       </c>
     </row>
     <row r="1345">
@@ -36942,7 +36942,7 @@
         <v>1</v>
       </c>
       <c r="G1345" t="n">
-        <v>0.04047976011994</v>
+        <v>0.0579710144927536</v>
       </c>
     </row>
     <row r="1346">
@@ -37049,7 +37049,7 @@
         <v>0</v>
       </c>
       <c r="G1350" t="n">
-        <v>0.0064967516241879</v>
+        <v>0.00849575212393803</v>
       </c>
     </row>
     <row r="1351">
@@ -37072,7 +37072,7 @@
         <v>0</v>
       </c>
       <c r="G1351" t="n">
-        <v>0.00249875062468766</v>
+        <v>0.00349825087456272</v>
       </c>
     </row>
     <row r="1352">
@@ -37183,7 +37183,7 @@
         <v>1</v>
       </c>
       <c r="G1356" t="n">
-        <v>0.0304847576211894</v>
+        <v>0.0359820089955022</v>
       </c>
     </row>
     <row r="1357">
@@ -37229,7 +37229,7 @@
         <v>1</v>
       </c>
       <c r="G1358" t="n">
-        <v>0.0144927536231884</v>
+        <v>0.0164917541229385</v>
       </c>
     </row>
     <row r="1359">
@@ -37275,7 +37275,7 @@
         <v>1</v>
       </c>
       <c r="G1360" t="n">
-        <v>0.0174912543728136</v>
+        <v>0.0149925037481259</v>
       </c>
     </row>
     <row r="1361">
@@ -37321,7 +37321,7 @@
         <v>0</v>
       </c>
       <c r="G1362" t="n">
-        <v>0.00949525237381309</v>
+        <v>0.0079960019990005</v>
       </c>
     </row>
     <row r="1363">
@@ -37344,7 +37344,7 @@
         <v>1</v>
       </c>
       <c r="G1363" t="n">
-        <v>0.623688155922039</v>
+        <v>0.621689155422289</v>
       </c>
     </row>
     <row r="1364">
@@ -37367,7 +37367,7 @@
         <v>1</v>
       </c>
       <c r="G1364" t="n">
-        <v>0.222888555722139</v>
+        <v>0.24087956021989</v>
       </c>
     </row>
     <row r="1365">
@@ -37390,7 +37390,7 @@
         <v>1</v>
       </c>
       <c r="G1365" t="n">
-        <v>0.000499750124937531</v>
+        <v>0.000999500249875062</v>
       </c>
     </row>
     <row r="1366">
@@ -37478,7 +37478,7 @@
         <v>1</v>
       </c>
       <c r="G1369" t="n">
-        <v>0.158420789605197</v>
+        <v>0.169415292353823</v>
       </c>
     </row>
     <row r="1370">
@@ -37608,7 +37608,7 @@
         <v>1</v>
       </c>
       <c r="G1375" t="n">
-        <v>0.228885557221389</v>
+        <v>0.238380809595202</v>
       </c>
     </row>
     <row r="1376">
@@ -37805,7 +37805,7 @@
         <v>1</v>
       </c>
       <c r="G1384" t="n">
-        <v>0.0414792603698151</v>
+        <v>0.0449775112443778</v>
       </c>
     </row>
     <row r="1385">
@@ -37870,7 +37870,7 @@
         <v>1</v>
       </c>
       <c r="G1387" t="n">
-        <v>0.0514742628685657</v>
+        <v>0.0464767616191904</v>
       </c>
     </row>
     <row r="1388">
@@ -37914,7 +37914,7 @@
         <v>1</v>
       </c>
       <c r="G1389" t="n">
-        <v>0.0284857571214393</v>
+        <v>0.0289855072463768</v>
       </c>
     </row>
     <row r="1390">
@@ -38128,7 +38128,7 @@
         <v>1</v>
       </c>
       <c r="G1399" t="n">
-        <v>0.360819590204898</v>
+        <v>0.358820589705147</v>
       </c>
     </row>
     <row r="1400">
@@ -38218,7 +38218,7 @@
         <v>1</v>
       </c>
       <c r="G1403" t="n">
-        <v>0.00499750124937531</v>
+        <v>0.00399800099950025</v>
       </c>
     </row>
     <row r="1404">
@@ -38241,7 +38241,7 @@
         <v>1</v>
       </c>
       <c r="G1404" t="n">
-        <v>0.137431284357821</v>
+        <v>0.154422788605697</v>
       </c>
     </row>
     <row r="1405">
@@ -38264,7 +38264,7 @@
         <v>1</v>
       </c>
       <c r="G1405" t="n">
-        <v>0.32783608195902</v>
+        <v>0.311344327836082</v>
       </c>
     </row>
     <row r="1406">
@@ -38308,7 +38308,7 @@
         <v>1</v>
       </c>
       <c r="G1407" t="n">
-        <v>0.146426786606697</v>
+        <v>0.142928535732134</v>
       </c>
     </row>
     <row r="1408">
@@ -38331,7 +38331,7 @@
         <v>1</v>
       </c>
       <c r="G1408" t="n">
-        <v>0.0999500249875062</v>
+        <v>0.105947026486757</v>
       </c>
     </row>
     <row r="1409">
@@ -38354,7 +38354,7 @@
         <v>1</v>
       </c>
       <c r="G1409" t="n">
-        <v>0.000499750124937531</v>
+        <v>0.00149925037481259</v>
       </c>
     </row>
     <row r="1410">
@@ -38419,7 +38419,7 @@
         <v>1</v>
       </c>
       <c r="G1412" t="n">
-        <v>0.452773613193403</v>
+        <v>0.438280859570215</v>
       </c>
     </row>
     <row r="1413">
@@ -38442,7 +38442,7 @@
         <v>1</v>
       </c>
       <c r="G1413" t="n">
-        <v>0.175412293853073</v>
+        <v>0.200899550224888</v>
       </c>
     </row>
     <row r="1414">
@@ -38488,7 +38488,7 @@
         <v>1</v>
       </c>
       <c r="G1415" t="n">
-        <v>0.0664667666166917</v>
+        <v>0.0624687656171914</v>
       </c>
     </row>
     <row r="1416">
@@ -38511,7 +38511,7 @@
         <v>1</v>
       </c>
       <c r="G1416" t="n">
-        <v>0.720139930034983</v>
+        <v>0.702148925537231</v>
       </c>
     </row>
     <row r="1417">
@@ -38534,7 +38534,7 @@
         <v>1</v>
       </c>
       <c r="G1417" t="n">
-        <v>0.000999500249875062</v>
+        <v>0.000499750124937531</v>
       </c>
     </row>
     <row r="1418">
@@ -38578,7 +38578,7 @@
         <v>1</v>
       </c>
       <c r="G1419" t="n">
-        <v>0.0269865067466267</v>
+        <v>0.0304847576211894</v>
       </c>
     </row>
     <row r="1420">
@@ -38622,7 +38622,7 @@
         <v>0</v>
       </c>
       <c r="G1421" t="n">
-        <v>0.00149925037481259</v>
+        <v>0.00199900049975012</v>
       </c>
     </row>
     <row r="1422">
@@ -38645,7 +38645,7 @@
         <v>1</v>
       </c>
       <c r="G1422" t="n">
-        <v>0.421289355322339</v>
+        <v>0.410794602698651</v>
       </c>
     </row>
     <row r="1423">
@@ -38668,7 +38668,7 @@
         <v>1</v>
       </c>
       <c r="G1423" t="n">
-        <v>0.0079960019990005</v>
+        <v>0.00349825087456272</v>
       </c>
     </row>
     <row r="1424">
@@ -38691,7 +38691,7 @@
         <v>1</v>
       </c>
       <c r="G1424" t="n">
-        <v>0.0199900049975013</v>
+        <v>0.0184907546226887</v>
       </c>
     </row>
     <row r="1425">
@@ -38737,7 +38737,7 @@
         <v>1</v>
       </c>
       <c r="G1426" t="n">
-        <v>0.178410794602699</v>
+        <v>0.170914542728636</v>
       </c>
     </row>
     <row r="1427">
@@ -38781,7 +38781,7 @@
         <v>1</v>
       </c>
       <c r="G1428" t="n">
-        <v>0.909545227386307</v>
+        <v>0.907046476761619</v>
       </c>
     </row>
     <row r="1429">
@@ -38804,7 +38804,7 @@
         <v>1</v>
       </c>
       <c r="G1429" t="n">
-        <v>0.606196901549225</v>
+        <v>0.628185907046477</v>
       </c>
     </row>
     <row r="1430">
@@ -38980,7 +38980,7 @@
         <v>1</v>
       </c>
       <c r="G1437" t="n">
-        <v>0.870564717641179</v>
+        <v>0.868565717141429</v>
       </c>
     </row>
     <row r="1438">
@@ -39070,7 +39070,7 @@
         <v>1</v>
       </c>
       <c r="G1441" t="n">
-        <v>0.31184407796102</v>
+        <v>0.338330834582709</v>
       </c>
     </row>
     <row r="1442">
@@ -39093,7 +39093,7 @@
         <v>1</v>
       </c>
       <c r="G1442" t="n">
-        <v>0.462768615692154</v>
+        <v>0.481259370314843</v>
       </c>
     </row>
     <row r="1443">
@@ -39116,7 +39116,7 @@
         <v>1</v>
       </c>
       <c r="G1443" t="n">
-        <v>0.164417791104448</v>
+        <v>0.168915542228886</v>
       </c>
     </row>
     <row r="1444">
@@ -39206,7 +39206,7 @@
         <v>1</v>
       </c>
       <c r="G1447" t="n">
-        <v>0.585207396301849</v>
+        <v>0.582708645677161</v>
       </c>
     </row>
     <row r="1448">
@@ -39229,7 +39229,7 @@
         <v>1</v>
       </c>
       <c r="G1448" t="n">
-        <v>0.0689655172413793</v>
+        <v>0.0669665167416292</v>
       </c>
     </row>
     <row r="1449">
@@ -39252,7 +39252,7 @@
         <v>1</v>
       </c>
       <c r="G1449" t="n">
-        <v>0.0064967516241879</v>
+        <v>0.00449775112443778</v>
       </c>
     </row>
     <row r="1450">
@@ -39361,7 +39361,7 @@
         <v>0</v>
       </c>
       <c r="G1454" t="n">
-        <v>0.0184907546226887</v>
+        <v>0.0169915042478761</v>
       </c>
     </row>
     <row r="1455">
@@ -39384,7 +39384,7 @@
         <v>1</v>
       </c>
       <c r="G1455" t="n">
-        <v>0.0104947526236882</v>
+        <v>0.0064967516241879</v>
       </c>
     </row>
     <row r="1456">
@@ -39407,7 +39407,7 @@
         <v>1</v>
       </c>
       <c r="G1456" t="n">
-        <v>0.039480259870065</v>
+        <v>0.0459770114942529</v>
       </c>
     </row>
     <row r="1457">
@@ -39453,7 +39453,7 @@
         <v>1</v>
       </c>
       <c r="G1458" t="n">
-        <v>0.242378810594703</v>
+        <v>0.24087956021989</v>
       </c>
     </row>
     <row r="1459">
@@ -39476,7 +39476,7 @@
         <v>1</v>
       </c>
       <c r="G1459" t="n">
-        <v>0.00549725137431284</v>
+        <v>0.00499750124937531</v>
       </c>
     </row>
     <row r="1460">
@@ -39499,7 +39499,7 @@
         <v>0</v>
       </c>
       <c r="G1460" t="n">
-        <v>0.0079960019990005</v>
+        <v>0.0144927536231884</v>
       </c>
     </row>
     <row r="1461">
@@ -39522,7 +39522,7 @@
         <v>1</v>
       </c>
       <c r="G1461" t="n">
-        <v>0.361319340329835</v>
+        <v>0.358820589705147</v>
       </c>
     </row>
     <row r="1462">
@@ -39545,7 +39545,7 @@
         <v>1</v>
       </c>
       <c r="G1462" t="n">
-        <v>0.188405797101449</v>
+        <v>0.2063968015992</v>
       </c>
     </row>
     <row r="1463">
@@ -39633,7 +39633,7 @@
         <v>1</v>
       </c>
       <c r="G1466" t="n">
-        <v>0.701149425287356</v>
+        <v>0.679660169915043</v>
       </c>
     </row>
     <row r="1467">
@@ -39677,7 +39677,7 @@
         <v>1</v>
       </c>
       <c r="G1468" t="n">
-        <v>0.0284857571214393</v>
+        <v>0.0349825087456272</v>
       </c>
     </row>
     <row r="1469">
@@ -39742,7 +39742,7 @@
         <v>1</v>
       </c>
       <c r="G1471" t="n">
-        <v>0.147926036981509</v>
+        <v>0.143928035982009</v>
       </c>
     </row>
     <row r="1472">
@@ -39786,7 +39786,7 @@
         <v>1</v>
       </c>
       <c r="G1473" t="n">
-        <v>0.00449775112443778</v>
+        <v>0.00549725137431284</v>
       </c>
     </row>
     <row r="1474">
@@ -39809,7 +39809,7 @@
         <v>1</v>
       </c>
       <c r="G1474" t="n">
-        <v>0.207896051974013</v>
+        <v>0.191404297851074</v>
       </c>
     </row>
     <row r="1475">
@@ -39832,7 +39832,7 @@
         <v>1</v>
       </c>
       <c r="G1475" t="n">
-        <v>0.0139930034982509</v>
+        <v>0.0114942528735632</v>
       </c>
     </row>
     <row r="1476">
@@ -39855,7 +39855,7 @@
         <v>1</v>
       </c>
       <c r="G1476" t="n">
-        <v>0.0189905047476262</v>
+        <v>0.0214892553723138</v>
       </c>
     </row>
     <row r="1477">
@@ -39878,7 +39878,7 @@
         <v>1</v>
       </c>
       <c r="G1477" t="n">
-        <v>0.0324837581209395</v>
+        <v>0.0274862568715642</v>
       </c>
     </row>
     <row r="1478">
@@ -39901,7 +39901,7 @@
         <v>1</v>
       </c>
       <c r="G1478" t="n">
-        <v>0.352823588205897</v>
+        <v>0.35432283858071</v>
       </c>
     </row>
     <row r="1479">
@@ -39945,7 +39945,7 @@
         <v>1</v>
       </c>
       <c r="G1480" t="n">
-        <v>0.232383808095952</v>
+        <v>0.222888555722139</v>
       </c>
     </row>
     <row r="1481">
@@ -40014,7 +40014,7 @@
         <v>0</v>
       </c>
       <c r="G1483" t="n">
-        <v>0.0299850074962519</v>
+        <v>0.0439780109945027</v>
       </c>
     </row>
     <row r="1484">
@@ -40060,7 +40060,7 @@
         <v>1</v>
       </c>
       <c r="G1485" t="n">
-        <v>0.906546726636682</v>
+        <v>0.896551724137931</v>
       </c>
     </row>
     <row r="1486">
@@ -40083,7 +40083,7 @@
         <v>1</v>
       </c>
       <c r="G1486" t="n">
-        <v>0.0559720139930035</v>
+        <v>0.056471764117941</v>
       </c>
     </row>
     <row r="1487">
@@ -40127,7 +40127,7 @@
         <v>0</v>
       </c>
       <c r="G1488" t="n">
-        <v>0.00249875062468766</v>
+        <v>0.00149925037481259</v>
       </c>
     </row>
     <row r="1489">
@@ -40150,7 +40150,7 @@
         <v>1</v>
       </c>
       <c r="G1489" t="n">
-        <v>0.00199900049975012</v>
+        <v>0.00249875062468766</v>
       </c>
     </row>
     <row r="1490">
@@ -40259,7 +40259,7 @@
         <v>1</v>
       </c>
       <c r="G1494" t="n">
-        <v>0.129435282358821</v>
+        <v>0.138930534732634</v>
       </c>
     </row>
     <row r="1495">
@@ -40282,7 +40282,7 @@
         <v>1</v>
       </c>
       <c r="G1495" t="n">
-        <v>0.242378810594703</v>
+        <v>0.232383808095952</v>
       </c>
     </row>
     <row r="1496">
@@ -40349,7 +40349,7 @@
         <v>1</v>
       </c>
       <c r="G1498" t="n">
-        <v>0.16791604197901</v>
+        <v>0.171414292853573</v>
       </c>
     </row>
     <row r="1499">
@@ -40372,7 +40372,7 @@
         <v>1</v>
       </c>
       <c r="G1499" t="n">
-        <v>0.205897051474263</v>
+        <v>0.195902048975512</v>
       </c>
     </row>
     <row r="1500">
@@ -40395,7 +40395,7 @@
         <v>1</v>
       </c>
       <c r="G1500" t="n">
-        <v>0.0109945027486257</v>
+        <v>0.0119940029985007</v>
       </c>
     </row>
     <row r="1501">
@@ -40418,7 +40418,7 @@
         <v>1</v>
       </c>
       <c r="G1501" t="n">
-        <v>0.0214892553723138</v>
+        <v>0.0219890054972514</v>
       </c>
     </row>
     <row r="1502">
@@ -40441,7 +40441,7 @@
         <v>1</v>
       </c>
       <c r="G1502" t="n">
-        <v>0.148425787106447</v>
+        <v>0.15992003998001</v>
       </c>
     </row>
     <row r="1503">
@@ -40464,7 +40464,7 @@
         <v>1</v>
       </c>
       <c r="G1503" t="n">
-        <v>0.503748125937031</v>
+        <v>0.510244877561219</v>
       </c>
     </row>
     <row r="1504">
@@ -40554,7 +40554,7 @@
         <v>1</v>
       </c>
       <c r="G1507" t="n">
-        <v>0.000499750124937531</v>
+        <v>0.000999500249875062</v>
       </c>
     </row>
     <row r="1508">
@@ -40621,7 +40621,7 @@
         <v>1</v>
       </c>
       <c r="G1510" t="n">
-        <v>0.0444777611194403</v>
+        <v>0.0344827586206897</v>
       </c>
     </row>
     <row r="1511">
@@ -40644,7 +40644,7 @@
         <v>1</v>
       </c>
       <c r="G1511" t="n">
-        <v>0.00699650174912544</v>
+        <v>0.00449775112443778</v>
       </c>
     </row>
     <row r="1512">
@@ -40667,7 +40667,7 @@
         <v>1</v>
       </c>
       <c r="G1512" t="n">
-        <v>0.864567716141929</v>
+        <v>0.866066966516742</v>
       </c>
     </row>
     <row r="1513">
@@ -40711,7 +40711,7 @@
         <v>1</v>
       </c>
       <c r="G1514" t="n">
-        <v>0.153423288355822</v>
+        <v>0.143428285857071</v>
       </c>
     </row>
     <row r="1515">
@@ -40734,7 +40734,7 @@
         <v>1</v>
       </c>
       <c r="G1515" t="n">
-        <v>0.031984007996002</v>
+        <v>0.0239880059970015</v>
       </c>
     </row>
     <row r="1516">
@@ -40799,7 +40799,7 @@
         <v>1</v>
       </c>
       <c r="G1518" t="n">
-        <v>0.145427286356822</v>
+        <v>0.153423288355822</v>
       </c>
     </row>
     <row r="1519">
@@ -40822,7 +40822,7 @@
         <v>1</v>
       </c>
       <c r="G1519" t="n">
-        <v>0.425787106446777</v>
+        <v>0.436781609195402</v>
       </c>
     </row>
     <row r="1520">
@@ -40845,7 +40845,7 @@
         <v>0</v>
       </c>
       <c r="G1520" t="n">
-        <v>0.00999500249875063</v>
+        <v>0.0139930034982509</v>
       </c>
     </row>
     <row r="1521">
@@ -40868,7 +40868,7 @@
         <v>1</v>
       </c>
       <c r="G1521" t="n">
-        <v>0.6071964017991</v>
+        <v>0.612193903048476</v>
       </c>
     </row>
     <row r="1522">
@@ -40935,7 +40935,7 @@
         <v>1</v>
       </c>
       <c r="G1524" t="n">
-        <v>0.00849575212393803</v>
+        <v>0.00749625187406297</v>
       </c>
     </row>
     <row r="1525">
@@ -41004,7 +41004,7 @@
         <v>1</v>
       </c>
       <c r="G1527" t="n">
-        <v>0.0224887556221889</v>
+        <v>0.0239880059970015</v>
       </c>
     </row>
     <row r="1528">
@@ -41027,7 +41027,7 @@
         <v>1</v>
       </c>
       <c r="G1528" t="n">
-        <v>0.000999500249875062</v>
+        <v>0.000499750124937531</v>
       </c>
     </row>
     <row r="1529">
@@ -41050,7 +41050,7 @@
         <v>0</v>
       </c>
       <c r="G1529" t="n">
-        <v>0.000999500249875062</v>
+        <v>0.000499750124937531</v>
       </c>
     </row>
     <row r="1530">
@@ -41140,7 +41140,7 @@
         <v>1</v>
       </c>
       <c r="G1533" t="n">
-        <v>0.00349825087456272</v>
+        <v>0.00149925037481259</v>
       </c>
     </row>
     <row r="1534">
@@ -41205,7 +41205,7 @@
         <v>1</v>
       </c>
       <c r="G1536" t="n">
-        <v>0.175912043978011</v>
+        <v>0.197401299350325</v>
       </c>
     </row>
     <row r="1537">
@@ -41293,7 +41293,7 @@
         <v>1</v>
       </c>
       <c r="G1540" t="n">
-        <v>0.102448775612194</v>
+        <v>0.111444277861069</v>
       </c>
     </row>
     <row r="1541">
@@ -41316,7 +41316,7 @@
         <v>1</v>
       </c>
       <c r="G1541" t="n">
-        <v>0.0249875062468766</v>
+        <v>0.0199900049975013</v>
       </c>
     </row>
     <row r="1542">
@@ -41339,7 +41339,7 @@
         <v>1</v>
       </c>
       <c r="G1542" t="n">
-        <v>0.47376311844078</v>
+        <v>0.489255372313843</v>
       </c>
     </row>
     <row r="1543">
@@ -41362,7 +41362,7 @@
         <v>1</v>
       </c>
       <c r="G1543" t="n">
-        <v>0.0174912543728136</v>
+        <v>0.0154922538730635</v>
       </c>
     </row>
     <row r="1544">
@@ -41385,7 +41385,7 @@
         <v>1</v>
       </c>
       <c r="G1544" t="n">
-        <v>0.302848575712144</v>
+        <v>0.297351324337831</v>
       </c>
     </row>
     <row r="1545">
@@ -41408,7 +41408,7 @@
         <v>0</v>
       </c>
       <c r="G1545" t="n">
-        <v>0.0264867566216892</v>
+        <v>0.0194902548725637</v>
       </c>
     </row>
     <row r="1546">
@@ -41431,7 +41431,7 @@
         <v>1</v>
       </c>
       <c r="G1546" t="n">
-        <v>0.00149925037481259</v>
+        <v>0.000999500249875062</v>
       </c>
     </row>
     <row r="1547">
@@ -41454,7 +41454,7 @@
         <v>1</v>
       </c>
       <c r="G1547" t="n">
-        <v>0.460769615192404</v>
+        <v>0.488255872063968</v>
       </c>
     </row>
     <row r="1548">
@@ -41477,7 +41477,7 @@
         <v>0</v>
       </c>
       <c r="G1548" t="n">
-        <v>0.27536231884058</v>
+        <v>0.261869065467266</v>
       </c>
     </row>
     <row r="1549">
@@ -41500,7 +41500,7 @@
         <v>1</v>
       </c>
       <c r="G1549" t="n">
-        <v>0.571214392803598</v>
+        <v>0.579210394802599</v>
       </c>
     </row>
     <row r="1550">
@@ -41588,7 +41588,7 @@
         <v>1</v>
       </c>
       <c r="G1553" t="n">
-        <v>0.423288355822089</v>
+        <v>0.3968015992004</v>
       </c>
     </row>
     <row r="1554">
@@ -41611,7 +41611,7 @@
         <v>1</v>
       </c>
       <c r="G1554" t="n">
-        <v>0.0494752623688156</v>
+        <v>0.0519740129935032</v>
       </c>
     </row>
     <row r="1555">
@@ -41697,7 +41697,7 @@
         <v>1</v>
       </c>
       <c r="G1558" t="n">
-        <v>0.295852073963018</v>
+        <v>0.288355822088956</v>
       </c>
     </row>
     <row r="1559">
@@ -41720,7 +41720,7 @@
         <v>1</v>
       </c>
       <c r="G1559" t="n">
-        <v>0.00699650174912544</v>
+        <v>0.00599700149925037</v>
       </c>
     </row>
     <row r="1560">
@@ -41875,7 +41875,7 @@
         <v>1</v>
       </c>
       <c r="G1566" t="n">
-        <v>0.135932033983008</v>
+        <v>0.129935032483758</v>
       </c>
     </row>
     <row r="1567">
@@ -41898,7 +41898,7 @@
         <v>1</v>
       </c>
       <c r="G1567" t="n">
-        <v>0.614692653673163</v>
+        <v>0.619690154922539</v>
       </c>
     </row>
     <row r="1568">
@@ -41965,7 +41965,7 @@
         <v>1</v>
       </c>
       <c r="G1570" t="n">
-        <v>0.00899550224887556</v>
+        <v>0.0119940029985007</v>
       </c>
     </row>
     <row r="1571">
@@ -41988,7 +41988,7 @@
         <v>1</v>
       </c>
       <c r="G1571" t="n">
-        <v>0.00999500249875063</v>
+        <v>0.00749625187406297</v>
       </c>
     </row>
     <row r="1572">
@@ -42011,7 +42011,7 @@
         <v>0</v>
       </c>
       <c r="G1572" t="n">
-        <v>0.00499750124937531</v>
+        <v>0.00149925037481259</v>
       </c>
     </row>
     <row r="1573">
@@ -42034,7 +42034,7 @@
         <v>1</v>
       </c>
       <c r="G1573" t="n">
-        <v>0.480259870064968</v>
+        <v>0.463768115942029</v>
       </c>
     </row>
     <row r="1574">
@@ -42057,7 +42057,7 @@
         <v>0</v>
       </c>
       <c r="G1574" t="n">
-        <v>0.00549725137431284</v>
+        <v>0.00599700149925037</v>
       </c>
     </row>
     <row r="1575">
@@ -42124,7 +42124,7 @@
         <v>1</v>
       </c>
       <c r="G1577" t="n">
-        <v>0.0584707646176912</v>
+        <v>0.0569715142428786</v>
       </c>
     </row>
     <row r="1578">
@@ -42147,7 +42147,7 @@
         <v>1</v>
       </c>
       <c r="G1578" t="n">
-        <v>0.8095952023988</v>
+        <v>0.792103948025987</v>
       </c>
     </row>
     <row r="1579">
@@ -42170,7 +42170,7 @@
         <v>1</v>
       </c>
       <c r="G1579" t="n">
-        <v>0.400299850074962</v>
+        <v>0.414792603698151</v>
       </c>
     </row>
     <row r="1580">
@@ -42283,7 +42283,7 @@
         <v>1</v>
       </c>
       <c r="G1584" t="n">
-        <v>0.00949525237381309</v>
+        <v>0.0119940029985007</v>
       </c>
     </row>
     <row r="1585">
@@ -42306,7 +42306,7 @@
         <v>1</v>
       </c>
       <c r="G1585" t="n">
-        <v>0.0499750124937531</v>
+        <v>0.0489755122438781</v>
       </c>
     </row>
     <row r="1586">
@@ -42350,7 +42350,7 @@
         <v>1</v>
       </c>
       <c r="G1587" t="n">
-        <v>0.000999500249875062</v>
+        <v>0.00349825087456272</v>
       </c>
     </row>
     <row r="1588">
@@ -42394,7 +42394,7 @@
         <v>0</v>
       </c>
       <c r="G1589" t="n">
-        <v>0.0399800099950025</v>
+        <v>0.0379810094952524</v>
       </c>
     </row>
     <row r="1590">
@@ -42417,7 +42417,7 @@
         <v>1</v>
       </c>
       <c r="G1590" t="n">
-        <v>0.486756621689155</v>
+        <v>0.484257871064468</v>
       </c>
     </row>
     <row r="1591">
@@ -42440,7 +42440,7 @@
         <v>1</v>
       </c>
       <c r="G1591" t="n">
-        <v>0.320339830084958</v>
+        <v>0.312343828085957</v>
       </c>
     </row>
     <row r="1592">
@@ -42463,7 +42463,7 @@
         <v>1</v>
       </c>
       <c r="G1592" t="n">
-        <v>0.190404797601199</v>
+        <v>0.202898550724638</v>
       </c>
     </row>
     <row r="1593">
@@ -42486,7 +42486,7 @@
         <v>0</v>
       </c>
       <c r="G1593" t="n">
-        <v>0.0109945027486257</v>
+        <v>0.00949525237381309</v>
       </c>
     </row>
     <row r="1594">
@@ -42509,7 +42509,7 @@
         <v>1</v>
       </c>
       <c r="G1594" t="n">
-        <v>0.0509745127436282</v>
+        <v>0.0519740129935032</v>
       </c>
     </row>
     <row r="1595">
@@ -42532,7 +42532,7 @@
         <v>1</v>
       </c>
       <c r="G1595" t="n">
-        <v>0.418290854572714</v>
+        <v>0.399300349825087</v>
       </c>
     </row>
     <row r="1596">
@@ -42555,7 +42555,7 @@
         <v>1</v>
       </c>
       <c r="G1596" t="n">
-        <v>0.000499750124937531</v>
+        <v>0.00149925037481259</v>
       </c>
     </row>
     <row r="1597">
@@ -42578,7 +42578,7 @@
         <v>1</v>
       </c>
       <c r="G1597" t="n">
-        <v>0.23488255872064</v>
+        <v>0.240379810094953</v>
       </c>
     </row>
     <row r="1598">
@@ -42601,7 +42601,7 @@
         <v>1</v>
       </c>
       <c r="G1598" t="n">
-        <v>0.0444777611194403</v>
+        <v>0.0469765117441279</v>
       </c>
     </row>
     <row r="1599">
@@ -42624,7 +42624,7 @@
         <v>1</v>
       </c>
       <c r="G1599" t="n">
-        <v>0.142928535732134</v>
+        <v>0.156421789105447</v>
       </c>
     </row>
     <row r="1600">
@@ -42647,7 +42647,7 @@
         <v>0</v>
       </c>
       <c r="G1600" t="n">
-        <v>0.0614692653673163</v>
+        <v>0.0609695152423788</v>
       </c>
     </row>
     <row r="1601">
@@ -42712,7 +42712,7 @@
         <v>1</v>
       </c>
       <c r="G1603" t="n">
-        <v>0.864567716141929</v>
+        <v>0.861069465267366</v>
       </c>
     </row>
     <row r="1604">
@@ -42756,7 +42756,7 @@
         <v>1</v>
       </c>
       <c r="G1605" t="n">
-        <v>0.596201899050475</v>
+        <v>0.598200899550225</v>
       </c>
     </row>
     <row r="1606">
@@ -42779,7 +42779,7 @@
         <v>1</v>
       </c>
       <c r="G1606" t="n">
-        <v>0.00449775112443778</v>
+        <v>0.0064967516241879</v>
       </c>
     </row>
     <row r="1607">
@@ -42802,7 +42802,7 @@
         <v>1</v>
       </c>
       <c r="G1607" t="n">
-        <v>0.0934532733633183</v>
+        <v>0.087456271864068</v>
       </c>
     </row>
     <row r="1608">
@@ -42825,7 +42825,7 @@
         <v>1</v>
       </c>
       <c r="G1608" t="n">
-        <v>0.00149925037481259</v>
+        <v>0.000999500249875062</v>
       </c>
     </row>
     <row r="1609">
@@ -42869,7 +42869,7 @@
         <v>1</v>
       </c>
       <c r="G1610" t="n">
-        <v>0.0434782608695652</v>
+        <v>0.047976011994003</v>
       </c>
     </row>
     <row r="1611">
@@ -42892,7 +42892,7 @@
         <v>1</v>
       </c>
       <c r="G1611" t="n">
-        <v>0.169915042478761</v>
+        <v>0.159420289855072</v>
       </c>
     </row>
     <row r="1612">
@@ -42938,7 +42938,7 @@
         <v>1</v>
       </c>
       <c r="G1613" t="n">
-        <v>0.00849575212393803</v>
+        <v>0.00399800099950025</v>
       </c>
     </row>
     <row r="1614">
@@ -42961,7 +42961,7 @@
         <v>1</v>
       </c>
       <c r="G1614" t="n">
-        <v>0.386306846576712</v>
+        <v>0.387806096951524</v>
       </c>
     </row>
     <row r="1615">
@@ -42984,7 +42984,7 @@
         <v>1</v>
       </c>
       <c r="G1615" t="n">
-        <v>0.00699650174912544</v>
+        <v>0.00899550224887556</v>
       </c>
     </row>
     <row r="1616">
@@ -43007,7 +43007,7 @@
         <v>1</v>
       </c>
       <c r="G1616" t="n">
-        <v>0.370814592703648</v>
+        <v>0.349325337331334</v>
       </c>
     </row>
     <row r="1617">
@@ -43030,7 +43030,7 @@
         <v>1</v>
       </c>
       <c r="G1617" t="n">
-        <v>0.499750124937531</v>
+        <v>0.507746126936532</v>
       </c>
     </row>
     <row r="1618">
@@ -43053,7 +43053,7 @@
         <v>1</v>
       </c>
       <c r="G1618" t="n">
-        <v>0.235882058970515</v>
+        <v>0.242378810594703</v>
       </c>
     </row>
     <row r="1619">
@@ -43097,7 +43097,7 @@
         <v>1</v>
       </c>
       <c r="G1620" t="n">
-        <v>0.180409795102449</v>
+        <v>0.201399300349825</v>
       </c>
     </row>
     <row r="1621">
@@ -43120,7 +43120,7 @@
         <v>1</v>
       </c>
       <c r="G1621" t="n">
-        <v>0.0144927536231884</v>
+        <v>0.0079960019990005</v>
       </c>
     </row>
     <row r="1622">
@@ -43143,7 +43143,7 @@
         <v>1</v>
       </c>
       <c r="G1622" t="n">
-        <v>0.0509745127436282</v>
+        <v>0.0469765117441279</v>
       </c>
     </row>
     <row r="1623">
@@ -43166,7 +43166,7 @@
         <v>0</v>
       </c>
       <c r="G1623" t="n">
-        <v>0.0819590204897551</v>
+        <v>0.0829585207396302</v>
       </c>
     </row>
     <row r="1624">
@@ -43233,7 +43233,7 @@
         <v>1</v>
       </c>
       <c r="G1626" t="n">
-        <v>0.162418790604698</v>
+        <v>0.144927536231884</v>
       </c>
     </row>
     <row r="1627">
@@ -43298,7 +43298,7 @@
         <v>0</v>
       </c>
       <c r="G1629" t="n">
-        <v>0.0304847576211894</v>
+        <v>0.024487756121939</v>
       </c>
     </row>
     <row r="1630">
@@ -43342,7 +43342,7 @@
         <v>1</v>
       </c>
       <c r="G1631" t="n">
-        <v>0.0529735132433783</v>
+        <v>0.0499750124937531</v>
       </c>
     </row>
     <row r="1632">
@@ -43365,7 +43365,7 @@
         <v>1</v>
       </c>
       <c r="G1632" t="n">
-        <v>0.163418290854573</v>
+        <v>0.164417791104448</v>
       </c>
     </row>
     <row r="1633">
@@ -43388,7 +43388,7 @@
         <v>1</v>
       </c>
       <c r="G1633" t="n">
-        <v>0.304847576211894</v>
+        <v>0.305347326336832</v>
       </c>
     </row>
     <row r="1634">
@@ -43432,7 +43432,7 @@
         <v>1</v>
       </c>
       <c r="G1635" t="n">
-        <v>0.0609695152423788</v>
+        <v>0.0634682658670665</v>
       </c>
     </row>
     <row r="1636">
@@ -43455,7 +43455,7 @@
         <v>1</v>
       </c>
       <c r="G1636" t="n">
-        <v>0.0314842578710645</v>
+        <v>0.0344827586206897</v>
       </c>
     </row>
     <row r="1637">
@@ -43522,7 +43522,7 @@
         <v>1</v>
       </c>
       <c r="G1639" t="n">
-        <v>0.238380809595202</v>
+        <v>0.247876061969015</v>
       </c>
     </row>
     <row r="1640">
@@ -43545,7 +43545,7 @@
         <v>1</v>
       </c>
       <c r="G1640" t="n">
-        <v>0.000999500249875062</v>
+        <v>0.00199900049975012</v>
       </c>
     </row>
     <row r="1641">
@@ -43568,7 +43568,7 @@
         <v>1</v>
       </c>
       <c r="G1641" t="n">
-        <v>0.239380309845077</v>
+        <v>0.227886056971514</v>
       </c>
     </row>
     <row r="1642">
@@ -43658,7 +43658,7 @@
         <v>1</v>
       </c>
       <c r="G1645" t="n">
-        <v>0.0534732633683158</v>
+        <v>0.0469765117441279</v>
       </c>
     </row>
     <row r="1646">
@@ -43792,7 +43792,7 @@
         <v>1</v>
       </c>
       <c r="G1651" t="n">
-        <v>0.00199900049975012</v>
+        <v>0.00149925037481259</v>
       </c>
     </row>
     <row r="1652">
@@ -43815,7 +43815,7 @@
         <v>1</v>
       </c>
       <c r="G1652" t="n">
-        <v>0.588705647176412</v>
+        <v>0.580709645177411</v>
       </c>
     </row>
     <row r="1653">
@@ -43838,7 +43838,7 @@
         <v>1</v>
       </c>
       <c r="G1653" t="n">
-        <v>0.00249875062468766</v>
+        <v>0.00149925037481259</v>
       </c>
     </row>
     <row r="1654">
@@ -43861,7 +43861,7 @@
         <v>1</v>
       </c>
       <c r="G1654" t="n">
-        <v>0.629185407296352</v>
+        <v>0.609195402298851</v>
       </c>
     </row>
     <row r="1655">
@@ -43928,7 +43928,7 @@
         <v>1</v>
       </c>
       <c r="G1657" t="n">
-        <v>0.0489755122438781</v>
+        <v>0.0459770114942529</v>
       </c>
     </row>
     <row r="1658">
@@ -43995,7 +43995,7 @@
         <v>1</v>
       </c>
       <c r="G1660" t="n">
-        <v>0.0859570214892554</v>
+        <v>0.087456271864068</v>
       </c>
     </row>
     <row r="1661">
@@ -44018,7 +44018,7 @@
         <v>1</v>
       </c>
       <c r="G1661" t="n">
-        <v>0.0689655172413793</v>
+        <v>0.0634682658670665</v>
       </c>
     </row>
     <row r="1662">
@@ -44041,7 +44041,7 @@
         <v>1</v>
       </c>
       <c r="G1662" t="n">
-        <v>0.00349825087456272</v>
+        <v>0.00199900049975012</v>
       </c>
     </row>
     <row r="1663">
@@ -44064,7 +44064,7 @@
         <v>1</v>
       </c>
       <c r="G1663" t="n">
-        <v>0.0224887556221889</v>
+        <v>0.0229885057471264</v>
       </c>
     </row>
     <row r="1664">
@@ -44087,7 +44087,7 @@
         <v>0</v>
       </c>
       <c r="G1664" t="n">
-        <v>0.00749625187406297</v>
+        <v>0.00549725137431284</v>
       </c>
     </row>
     <row r="1665">
@@ -44110,7 +44110,7 @@
         <v>1</v>
       </c>
       <c r="G1665" t="n">
-        <v>0.658170914542729</v>
+        <v>0.681159420289855</v>
       </c>
     </row>
     <row r="1666">
@@ -44133,7 +44133,7 @@
         <v>1</v>
       </c>
       <c r="G1666" t="n">
-        <v>0.5912043978011</v>
+        <v>0.612693653173413</v>
       </c>
     </row>
     <row r="1667">
@@ -44156,7 +44156,7 @@
         <v>1</v>
       </c>
       <c r="G1667" t="n">
-        <v>0.00399800099950025</v>
+        <v>0.0064967516241879</v>
       </c>
     </row>
     <row r="1668">
@@ -44179,7 +44179,7 @@
         <v>1</v>
       </c>
       <c r="G1668" t="n">
-        <v>0.510744627686157</v>
+        <v>0.490754622688656</v>
       </c>
     </row>
     <row r="1669">
@@ -44202,7 +44202,7 @@
         <v>1</v>
       </c>
       <c r="G1669" t="n">
-        <v>0.0104947526236882</v>
+        <v>0.0139930034982509</v>
       </c>
     </row>
     <row r="1670">
@@ -44271,7 +44271,7 @@
         <v>1</v>
       </c>
       <c r="G1672" t="n">
-        <v>0.0079960019990005</v>
+        <v>0.00699650174912544</v>
       </c>
     </row>
     <row r="1673">
@@ -44317,7 +44317,7 @@
         <v>1</v>
       </c>
       <c r="G1674" t="n">
-        <v>0.124437781109445</v>
+        <v>0.166916541729135</v>
       </c>
     </row>
     <row r="1675">
@@ -44340,7 +44340,7 @@
         <v>1</v>
       </c>
       <c r="G1675" t="n">
-        <v>0.0464767616191904</v>
+        <v>0.0439780109945027</v>
       </c>
     </row>
     <row r="1676">
@@ -44363,7 +44363,7 @@
         <v>1</v>
       </c>
       <c r="G1676" t="n">
-        <v>0.00149925037481259</v>
+        <v>0.00349825087456272</v>
       </c>
     </row>
     <row r="1677">
@@ -44407,7 +44407,7 @@
         <v>0</v>
       </c>
       <c r="G1678" t="n">
-        <v>0.476261869065467</v>
+        <v>0.461769115442279</v>
       </c>
     </row>
     <row r="1679">
@@ -44430,7 +44430,7 @@
         <v>1</v>
       </c>
       <c r="G1679" t="n">
-        <v>0.0664667666166917</v>
+        <v>0.0734632683658171</v>
       </c>
     </row>
     <row r="1680">
@@ -44453,7 +44453,7 @@
         <v>1</v>
       </c>
       <c r="G1680" t="n">
-        <v>0.743628185907046</v>
+        <v>0.749125437281359</v>
       </c>
     </row>
     <row r="1681">
@@ -44476,7 +44476,7 @@
         <v>1</v>
       </c>
       <c r="G1681" t="n">
-        <v>0.00949525237381309</v>
+        <v>0.00499750124937531</v>
       </c>
     </row>
     <row r="1682">
@@ -44522,7 +44522,7 @@
         <v>1</v>
       </c>
       <c r="G1683" t="n">
-        <v>0.348325837081459</v>
+        <v>0.352823588205897</v>
       </c>
     </row>
     <row r="1684">
@@ -44587,7 +44587,7 @@
         <v>1</v>
       </c>
       <c r="G1686" t="n">
-        <v>0.00449775112443778</v>
+        <v>0.00349825087456272</v>
       </c>
     </row>
     <row r="1687">
@@ -44610,7 +44610,7 @@
         <v>0</v>
       </c>
       <c r="G1687" t="n">
-        <v>0.00299850074962519</v>
+        <v>0.00149925037481259</v>
       </c>
     </row>
     <row r="1688">
@@ -44656,7 +44656,7 @@
         <v>1</v>
       </c>
       <c r="G1689" t="n">
-        <v>0.00549725137431284</v>
+        <v>0.00899550224887556</v>
       </c>
     </row>
     <row r="1690">
@@ -44723,7 +44723,7 @@
         <v>1</v>
       </c>
       <c r="G1692" t="n">
-        <v>0.201399300349825</v>
+        <v>0.209895052473763</v>
       </c>
     </row>
     <row r="1693">
@@ -44811,7 +44811,7 @@
         <v>0</v>
       </c>
       <c r="G1696" t="n">
-        <v>0.425287356321839</v>
+        <v>0.404297851074463</v>
       </c>
     </row>
     <row r="1697">
@@ -44878,7 +44878,7 @@
         <v>1</v>
       </c>
       <c r="G1699" t="n">
-        <v>0.756121939030485</v>
+        <v>0.747626186906547</v>
       </c>
     </row>
     <row r="1700">
@@ -44901,7 +44901,7 @@
         <v>1</v>
       </c>
       <c r="G1700" t="n">
-        <v>0.137931034482759</v>
+        <v>0.122938530734633</v>
       </c>
     </row>
     <row r="1701">
@@ -44991,7 +44991,7 @@
         <v>1</v>
       </c>
       <c r="G1704" t="n">
-        <v>0.251374312843578</v>
+        <v>0.243378310844578</v>
       </c>
     </row>
     <row r="1705">
@@ -45014,7 +45014,7 @@
         <v>1</v>
       </c>
       <c r="G1705" t="n">
-        <v>0.16791604197901</v>
+        <v>0.16191904047976</v>
       </c>
     </row>
     <row r="1706">
@@ -45037,7 +45037,7 @@
         <v>0</v>
       </c>
       <c r="G1706" t="n">
-        <v>0.0214892553723138</v>
+        <v>0.0189905047476262</v>
       </c>
     </row>
     <row r="1707">
@@ -45060,7 +45060,7 @@
         <v>1</v>
       </c>
       <c r="G1707" t="n">
-        <v>0.0259870064967516</v>
+        <v>0.0209895052473763</v>
       </c>
     </row>
     <row r="1708">
@@ -45215,7 +45215,7 @@
         <v>1</v>
       </c>
       <c r="G1714" t="n">
-        <v>0.31784107946027</v>
+        <v>0.318840579710145</v>
       </c>
     </row>
     <row r="1715">
@@ -45303,7 +45303,7 @@
         <v>1</v>
       </c>
       <c r="G1718" t="n">
-        <v>0.000999500249875062</v>
+        <v>0.000499750124937531</v>
       </c>
     </row>
     <row r="1719">
@@ -45347,7 +45347,7 @@
         <v>1</v>
       </c>
       <c r="G1720" t="n">
-        <v>0.374812593703148</v>
+        <v>0.386806596701649</v>
       </c>
     </row>
     <row r="1721">
@@ -45412,7 +45412,7 @@
         <v>1</v>
       </c>
       <c r="G1723" t="n">
-        <v>0.0594702648675662</v>
+        <v>0.0629685157421289</v>
       </c>
     </row>
     <row r="1724">
@@ -45435,7 +45435,7 @@
         <v>1</v>
       </c>
       <c r="G1724" t="n">
-        <v>0.889055472263868</v>
+        <v>0.906546726636682</v>
       </c>
     </row>
     <row r="1725">
@@ -45458,7 +45458,7 @@
         <v>1</v>
       </c>
       <c r="G1725" t="n">
-        <v>0.371314342828586</v>
+        <v>0.384807596201899</v>
       </c>
     </row>
     <row r="1726">
@@ -45523,7 +45523,7 @@
         <v>1</v>
       </c>
       <c r="G1728" t="n">
-        <v>0.367816091954023</v>
+        <v>0.373313343328336</v>
       </c>
     </row>
     <row r="1729">
@@ -45546,7 +45546,7 @@
         <v>1</v>
       </c>
       <c r="G1729" t="n">
-        <v>0.898050974512744</v>
+        <v>0.884057971014493</v>
       </c>
     </row>
     <row r="1730">
@@ -45657,7 +45657,7 @@
         <v>1</v>
       </c>
       <c r="G1734" t="n">
-        <v>0.0694652673663168</v>
+        <v>0.0649675162418791</v>
       </c>
     </row>
     <row r="1735">
@@ -45680,7 +45680,7 @@
         <v>1</v>
       </c>
       <c r="G1735" t="n">
-        <v>0.869565217391304</v>
+        <v>0.867566216891554</v>
       </c>
     </row>
     <row r="1736">
@@ -45766,7 +45766,7 @@
         <v>0</v>
       </c>
       <c r="G1739" t="n">
-        <v>0.00199900049975012</v>
+        <v>0.00149925037481259</v>
       </c>
     </row>
     <row r="1740">
@@ -45789,7 +45789,7 @@
         <v>1</v>
       </c>
       <c r="G1740" t="n">
-        <v>0.00349825087456272</v>
+        <v>0.00149925037481259</v>
       </c>
     </row>
     <row r="1741">
@@ -45833,7 +45833,7 @@
         <v>1</v>
       </c>
       <c r="G1742" t="n">
-        <v>0.056471764117941</v>
+        <v>0.0569715142428786</v>
       </c>
     </row>
     <row r="1743">
@@ -45856,7 +45856,7 @@
         <v>1</v>
       </c>
       <c r="G1743" t="n">
-        <v>0.0444777611194403</v>
+        <v>0.0499750124937531</v>
       </c>
     </row>
     <row r="1744">
@@ -45879,7 +45879,7 @@
         <v>1</v>
       </c>
       <c r="G1744" t="n">
-        <v>0.323338330834583</v>
+        <v>0.312843578210895</v>
       </c>
     </row>
     <row r="1745">
@@ -45990,7 +45990,7 @@
         <v>1</v>
       </c>
       <c r="G1749" t="n">
-        <v>0.5912043978011</v>
+        <v>0.616691654172913</v>
       </c>
     </row>
     <row r="1750">
@@ -46013,7 +46013,7 @@
         <v>1</v>
       </c>
       <c r="G1750" t="n">
-        <v>0.0604697651174413</v>
+        <v>0.071464267866067</v>
       </c>
     </row>
     <row r="1751">
@@ -46036,7 +46036,7 @@
         <v>1</v>
       </c>
       <c r="G1751" t="n">
-        <v>0.0199900049975013</v>
+        <v>0.0134932533733133</v>
       </c>
     </row>
     <row r="1752">
@@ -46059,7 +46059,7 @@
         <v>1</v>
       </c>
       <c r="G1752" t="n">
-        <v>0.00349825087456272</v>
+        <v>0.00549725137431284</v>
       </c>
     </row>
     <row r="1753">
@@ -46103,7 +46103,7 @@
         <v>1</v>
       </c>
       <c r="G1754" t="n">
-        <v>0.35832083958021</v>
+        <v>0.377811094452774</v>
       </c>
     </row>
     <row r="1755">
@@ -46126,7 +46126,7 @@
         <v>0</v>
       </c>
       <c r="G1755" t="n">
-        <v>0.00149925037481259</v>
+        <v>0.000499750124937531</v>
       </c>
     </row>
     <row r="1756">
@@ -46172,7 +46172,7 @@
         <v>1</v>
       </c>
       <c r="G1757" t="n">
-        <v>0.0409795102448776</v>
+        <v>0.0429785107446277</v>
       </c>
     </row>
     <row r="1758">
@@ -46195,7 +46195,7 @@
         <v>1</v>
       </c>
       <c r="G1758" t="n">
-        <v>0.000499750124937531</v>
+        <v>0.000999500249875062</v>
       </c>
     </row>
     <row r="1759">
@@ -46218,7 +46218,7 @@
         <v>1</v>
       </c>
       <c r="G1759" t="n">
-        <v>0.604697651174413</v>
+        <v>0.604197901049475</v>
       </c>
     </row>
     <row r="1760">
@@ -46304,7 +46304,7 @@
         <v>1</v>
       </c>
       <c r="G1763" t="n">
-        <v>0.00699650174912544</v>
+        <v>0.00349825087456272</v>
       </c>
     </row>
     <row r="1764">
@@ -46327,7 +46327,7 @@
         <v>1</v>
       </c>
       <c r="G1764" t="n">
-        <v>0.902548725637181</v>
+        <v>0.894052973513243</v>
       </c>
     </row>
     <row r="1765">
@@ -46371,7 +46371,7 @@
         <v>1</v>
       </c>
       <c r="G1766" t="n">
-        <v>0.00149925037481259</v>
+        <v>0.000499750124937531</v>
       </c>
     </row>
     <row r="1767">
@@ -46394,7 +46394,7 @@
         <v>1</v>
       </c>
       <c r="G1767" t="n">
-        <v>0.504747626186906</v>
+        <v>0.471764117941029</v>
       </c>
     </row>
     <row r="1768">
@@ -46440,7 +46440,7 @@
         <v>1</v>
       </c>
       <c r="G1769" t="n">
-        <v>0.602198900549725</v>
+        <v>0.600199900049975</v>
       </c>
     </row>
     <row r="1770">
@@ -46484,7 +46484,7 @@
         <v>1</v>
       </c>
       <c r="G1771" t="n">
-        <v>0.330834582708646</v>
+        <v>0.345827086456772</v>
       </c>
     </row>
     <row r="1772">
@@ -46507,7 +46507,7 @@
         <v>1</v>
       </c>
       <c r="G1772" t="n">
-        <v>0.952023988005997</v>
+        <v>0.942528735632184</v>
       </c>
     </row>
     <row r="1773">
@@ -46530,7 +46530,7 @@
         <v>0</v>
       </c>
       <c r="G1773" t="n">
-        <v>0.235882058970515</v>
+        <v>0.240379810094953</v>
       </c>
     </row>
     <row r="1774">
@@ -46574,7 +46574,7 @@
         <v>1</v>
       </c>
       <c r="G1775" t="n">
-        <v>0.00349825087456272</v>
+        <v>0.00549725137431284</v>
       </c>
     </row>
     <row r="1776">
@@ -46618,7 +46618,7 @@
         <v>1</v>
       </c>
       <c r="G1777" t="n">
-        <v>0.495252373813093</v>
+        <v>0.491754122938531</v>
       </c>
     </row>
     <row r="1778">
@@ -46641,7 +46641,7 @@
         <v>1</v>
       </c>
       <c r="G1778" t="n">
-        <v>0.0109945027486257</v>
+        <v>0.0149925037481259</v>
       </c>
     </row>
     <row r="1779">
@@ -46664,7 +46664,7 @@
         <v>1</v>
       </c>
       <c r="G1779" t="n">
-        <v>0.0379810094952524</v>
+        <v>0.0374812593703148</v>
       </c>
     </row>
     <row r="1780">
@@ -46687,7 +46687,7 @@
         <v>1</v>
       </c>
       <c r="G1780" t="n">
-        <v>0.015992003998001</v>
+        <v>0.0144927536231884</v>
       </c>
     </row>
     <row r="1781">
@@ -46775,7 +46775,7 @@
         <v>1</v>
       </c>
       <c r="G1784" t="n">
-        <v>0.0219890054972514</v>
+        <v>0.0189905047476262</v>
       </c>
     </row>
     <row r="1785">
@@ -46842,7 +46842,7 @@
         <v>1</v>
       </c>
       <c r="G1787" t="n">
-        <v>0.000499750124937531</v>
+        <v>0.000999500249875062</v>
       </c>
     </row>
     <row r="1788">
@@ -46886,7 +46886,7 @@
         <v>1</v>
       </c>
       <c r="G1789" t="n">
-        <v>0.0999500249875062</v>
+        <v>0.0974512743628186</v>
       </c>
     </row>
     <row r="1790">
@@ -46909,7 +46909,7 @@
         <v>1</v>
       </c>
       <c r="G1790" t="n">
-        <v>0.0124937531234383</v>
+        <v>0.015992003998001</v>
       </c>
     </row>
     <row r="1791">
@@ -46955,7 +46955,7 @@
         <v>1</v>
       </c>
       <c r="G1792" t="n">
-        <v>0.0514742628685657</v>
+        <v>0.0389805097451274</v>
       </c>
     </row>
     <row r="1793">
@@ -46978,7 +46978,7 @@
         <v>1</v>
       </c>
       <c r="G1793" t="n">
-        <v>0.0574712643678161</v>
+        <v>0.0664667666166917</v>
       </c>
     </row>
     <row r="1794">
@@ -47001,7 +47001,7 @@
         <v>1</v>
       </c>
       <c r="G1794" t="n">
-        <v>0.614192903548226</v>
+        <v>0.596701649175412</v>
       </c>
     </row>
     <row r="1795">
@@ -47070,7 +47070,7 @@
         <v>1</v>
       </c>
       <c r="G1797" t="n">
-        <v>0.0579710144927536</v>
+        <v>0.0634682658670665</v>
       </c>
     </row>
     <row r="1798">
@@ -47139,7 +47139,7 @@
         <v>1</v>
       </c>
       <c r="G1800" t="n">
-        <v>0.088455772113943</v>
+        <v>0.101449275362319</v>
       </c>
     </row>
     <row r="1801">
@@ -47162,7 +47162,7 @@
         <v>0</v>
       </c>
       <c r="G1801" t="n">
-        <v>0.12343828085957</v>
+        <v>0.137431284357821</v>
       </c>
     </row>
     <row r="1802">
@@ -47300,7 +47300,7 @@
         <v>1</v>
       </c>
       <c r="G1807" t="n">
-        <v>0.00149925037481259</v>
+        <v>0.000999500249875062</v>
       </c>
     </row>
     <row r="1808">
@@ -47323,7 +47323,7 @@
         <v>1</v>
       </c>
       <c r="G1808" t="n">
-        <v>0.0519740129935032</v>
+        <v>0.0494752623688156</v>
       </c>
     </row>
     <row r="1809">
@@ -47457,7 +47457,7 @@
         <v>1</v>
       </c>
       <c r="G1814" t="n">
-        <v>0.0519740129935032</v>
+        <v>0.0569715142428786</v>
       </c>
     </row>
     <row r="1815">
@@ -47480,7 +47480,7 @@
         <v>1</v>
       </c>
       <c r="G1815" t="n">
-        <v>0.0424787606196902</v>
+        <v>0.0364817591204398</v>
       </c>
     </row>
     <row r="1816">
@@ -47566,7 +47566,7 @@
         <v>1</v>
       </c>
       <c r="G1819" t="n">
-        <v>0.48575712143928</v>
+        <v>0.497251374312844</v>
       </c>
     </row>
     <row r="1820">
@@ -47652,7 +47652,7 @@
         <v>1</v>
       </c>
       <c r="G1823" t="n">
-        <v>0.244377811094453</v>
+        <v>0.230384807596202</v>
       </c>
     </row>
     <row r="1824">
@@ -47719,7 +47719,7 @@
         <v>1</v>
       </c>
       <c r="G1826" t="n">
-        <v>0.023488255872064</v>
+        <v>0.0314842578710645</v>
       </c>
     </row>
     <row r="1827">
@@ -47742,7 +47742,7 @@
         <v>1</v>
       </c>
       <c r="G1827" t="n">
-        <v>0.0174912543728136</v>
+        <v>0.015992003998001</v>
       </c>
     </row>
     <row r="1828">
@@ -47853,7 +47853,7 @@
         <v>1</v>
       </c>
       <c r="G1832" t="n">
-        <v>0.0109945027486257</v>
+        <v>0.0124937531234383</v>
       </c>
     </row>
     <row r="1833">
@@ -47899,7 +47899,7 @@
         <v>1</v>
       </c>
       <c r="G1834" t="n">
-        <v>0.192903548225887</v>
+        <v>0.16391804097951</v>
       </c>
     </row>
     <row r="1835">
@@ -47943,7 +47943,7 @@
         <v>1</v>
       </c>
       <c r="G1836" t="n">
-        <v>0.0399800099950025</v>
+        <v>0.0469765117441279</v>
       </c>
     </row>
     <row r="1837">
@@ -47966,7 +47966,7 @@
         <v>1</v>
       </c>
       <c r="G1837" t="n">
-        <v>0.221389305347326</v>
+        <v>0.23888055972014</v>
       </c>
     </row>
     <row r="1838">
@@ -48010,7 +48010,7 @@
         <v>1</v>
       </c>
       <c r="G1839" t="n">
-        <v>0.673163418290855</v>
+        <v>0.679660169915043</v>
       </c>
     </row>
     <row r="1840">
@@ -48098,7 +48098,7 @@
         <v>1</v>
       </c>
       <c r="G1843" t="n">
-        <v>0.0129935032483758</v>
+        <v>0.0104947526236882</v>
       </c>
     </row>
     <row r="1844">
@@ -48163,7 +48163,7 @@
         <v>1</v>
       </c>
       <c r="G1846" t="n">
-        <v>0.802098950524738</v>
+        <v>0.789105447276362</v>
       </c>
     </row>
     <row r="1847">
@@ -48251,7 +48251,7 @@
         <v>1</v>
       </c>
       <c r="G1850" t="n">
-        <v>0.0349825087456272</v>
+        <v>0.0254872563718141</v>
       </c>
     </row>
     <row r="1851">
@@ -48274,7 +48274,7 @@
         <v>1</v>
       </c>
       <c r="G1851" t="n">
-        <v>0.783608195902049</v>
+        <v>0.773613193403298</v>
       </c>
     </row>
     <row r="1852">
@@ -48318,7 +48318,7 @@
         <v>1</v>
       </c>
       <c r="G1853" t="n">
-        <v>0.824587706146927</v>
+        <v>0.847076461769115</v>
       </c>
     </row>
     <row r="1854">
@@ -48341,7 +48341,7 @@
         <v>1</v>
       </c>
       <c r="G1854" t="n">
-        <v>0.102948525737131</v>
+        <v>0.110944527736132</v>
       </c>
     </row>
     <row r="1855">
@@ -48364,7 +48364,7 @@
         <v>1</v>
       </c>
       <c r="G1855" t="n">
-        <v>0.176411794102949</v>
+        <v>0.179410294852574</v>
       </c>
     </row>
     <row r="1856">
@@ -48387,7 +48387,7 @@
         <v>1</v>
       </c>
       <c r="G1856" t="n">
-        <v>0.00199900049975012</v>
+        <v>0.00249875062468766</v>
       </c>
     </row>
     <row r="1857">
@@ -48410,7 +48410,7 @@
         <v>1</v>
       </c>
       <c r="G1857" t="n">
-        <v>0.137431284357821</v>
+        <v>0.135432283858071</v>
       </c>
     </row>
     <row r="1858">
@@ -48433,7 +48433,7 @@
         <v>1</v>
       </c>
       <c r="G1858" t="n">
-        <v>0.180409795102449</v>
+        <v>0.197401299350325</v>
       </c>
     </row>
     <row r="1859">
@@ -48479,7 +48479,7 @@
         <v>1</v>
       </c>
       <c r="G1860" t="n">
-        <v>0.23288355822089</v>
+        <v>0.222888555722139</v>
       </c>
     </row>
     <row r="1861">
@@ -48523,7 +48523,7 @@
         <v>0</v>
       </c>
       <c r="G1862" t="n">
-        <v>0.023488255872064</v>
+        <v>0.0199900049975013</v>
       </c>
     </row>
     <row r="1863">
@@ -48546,7 +48546,7 @@
         <v>1</v>
       </c>
       <c r="G1863" t="n">
-        <v>0.0439780109945027</v>
+        <v>0.0504747626186907</v>
       </c>
     </row>
     <row r="1864">
@@ -48569,7 +48569,7 @@
         <v>1</v>
       </c>
       <c r="G1864" t="n">
-        <v>0.623188405797101</v>
+        <v>0.605697151424288</v>
       </c>
     </row>
     <row r="1865">
@@ -48615,7 +48615,7 @@
         <v>1</v>
       </c>
       <c r="G1866" t="n">
-        <v>0.171414292853573</v>
+        <v>0.169415292353823</v>
       </c>
     </row>
     <row r="1867">
@@ -48638,7 +48638,7 @@
         <v>1</v>
       </c>
       <c r="G1867" t="n">
-        <v>0.0104947526236882</v>
+        <v>0.0149925037481259</v>
       </c>
     </row>
     <row r="1868">
@@ -48661,7 +48661,7 @@
         <v>1</v>
       </c>
       <c r="G1868" t="n">
-        <v>0.00849575212393803</v>
+        <v>0.0139930034982509</v>
       </c>
     </row>
     <row r="1869">
@@ -48707,7 +48707,7 @@
         <v>1</v>
       </c>
       <c r="G1870" t="n">
-        <v>0.621689155422289</v>
+        <v>0.603698150924538</v>
       </c>
     </row>
     <row r="1871">
@@ -48751,7 +48751,7 @@
         <v>1</v>
       </c>
       <c r="G1872" t="n">
-        <v>0.00299850074962519</v>
+        <v>0.00249875062468766</v>
       </c>
     </row>
     <row r="1873">
@@ -48795,7 +48795,7 @@
         <v>1</v>
       </c>
       <c r="G1874" t="n">
-        <v>0.000999500249875062</v>
+        <v>0.000499750124937531</v>
       </c>
     </row>
     <row r="1875">
@@ -48818,7 +48818,7 @@
         <v>1</v>
       </c>
       <c r="G1875" t="n">
-        <v>0.100449775112444</v>
+        <v>0.101949025487256</v>
       </c>
     </row>
     <row r="1876">
@@ -48862,7 +48862,7 @@
         <v>1</v>
       </c>
       <c r="G1877" t="n">
-        <v>0.109945027486257</v>
+        <v>0.110944527736132</v>
       </c>
     </row>
     <row r="1878">
@@ -48885,7 +48885,7 @@
         <v>1</v>
       </c>
       <c r="G1878" t="n">
-        <v>0.161419290354823</v>
+        <v>0.152423788105947</v>
       </c>
     </row>
     <row r="1879">
@@ -48931,7 +48931,7 @@
         <v>1</v>
       </c>
       <c r="G1880" t="n">
-        <v>0.439780109945027</v>
+        <v>0.449775112443778</v>
       </c>
     </row>
     <row r="1881">
@@ -48954,7 +48954,7 @@
         <v>1</v>
       </c>
       <c r="G1881" t="n">
-        <v>0.000999500249875062</v>
+        <v>0.00249875062468766</v>
       </c>
     </row>
     <row r="1882">
@@ -49000,7 +49000,7 @@
         <v>1</v>
       </c>
       <c r="G1883" t="n">
-        <v>0.0464767616191904</v>
+        <v>0.0484757621189405</v>
       </c>
     </row>
     <row r="1884">
@@ -49023,7 +49023,7 @@
         <v>1</v>
       </c>
       <c r="G1884" t="n">
-        <v>0.182408795602199</v>
+        <v>0.177911044477761</v>
       </c>
     </row>
     <row r="1885">
@@ -49067,7 +49067,7 @@
         <v>1</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.39880059970015</v>
+        <v>0.410794602698651</v>
       </c>
     </row>
     <row r="1887">
@@ -49134,7 +49134,7 @@
         <v>1</v>
       </c>
       <c r="G1889" t="n">
-        <v>0.0134932533733133</v>
+        <v>0.0114942528735632</v>
       </c>
     </row>
     <row r="1890">
@@ -49157,7 +49157,7 @@
         <v>0</v>
       </c>
       <c r="G1890" t="n">
-        <v>0.0529735132433783</v>
+        <v>0.0474762618690655</v>
       </c>
     </row>
     <row r="1891">
@@ -49201,7 +49201,7 @@
         <v>1</v>
       </c>
       <c r="G1892" t="n">
-        <v>0.253873063468266</v>
+        <v>0.244377811094453</v>
       </c>
     </row>
     <row r="1893">
@@ -49289,7 +49289,7 @@
         <v>1</v>
       </c>
       <c r="G1896" t="n">
-        <v>0.00299850074962519</v>
+        <v>0.00199900049975012</v>
       </c>
     </row>
     <row r="1897">
@@ -49333,7 +49333,7 @@
         <v>1</v>
       </c>
       <c r="G1898" t="n">
-        <v>0.147926036981509</v>
+        <v>0.148425787106447</v>
       </c>
     </row>
     <row r="1899">
@@ -49356,7 +49356,7 @@
         <v>1</v>
       </c>
       <c r="G1899" t="n">
-        <v>0.596701649175412</v>
+        <v>0.585707146426787</v>
       </c>
     </row>
     <row r="1900">
@@ -49400,7 +49400,7 @@
         <v>1</v>
       </c>
       <c r="G1901" t="n">
-        <v>0.00299850074962519</v>
+        <v>0.00349825087456272</v>
       </c>
     </row>
     <row r="1902">
@@ -49423,7 +49423,7 @@
         <v>0</v>
       </c>
       <c r="G1902" t="n">
-        <v>0.00149925037481259</v>
+        <v>0.000499750124937531</v>
       </c>
     </row>
     <row r="1903">
@@ -49446,7 +49446,7 @@
         <v>1</v>
       </c>
       <c r="G1903" t="n">
-        <v>0.28135932033983</v>
+        <v>0.291354322838581</v>
       </c>
     </row>
     <row r="1904">
@@ -49469,7 +49469,7 @@
         <v>1</v>
       </c>
       <c r="G1904" t="n">
-        <v>0.209395302348826</v>
+        <v>0.203898050974513</v>
       </c>
     </row>
     <row r="1905">
@@ -49492,7 +49492,7 @@
         <v>0</v>
       </c>
       <c r="G1905" t="n">
-        <v>0.0354822588705647</v>
+        <v>0.0334832583708146</v>
       </c>
     </row>
     <row r="1906">
@@ -49515,7 +49515,7 @@
         <v>1</v>
       </c>
       <c r="G1906" t="n">
-        <v>0.00149925037481259</v>
+        <v>0.00199900049975012</v>
       </c>
     </row>
     <row r="1907">
@@ -49538,7 +49538,7 @@
         <v>1</v>
       </c>
       <c r="G1907" t="n">
-        <v>0.0129935032483758</v>
+        <v>0.0114942528735632</v>
       </c>
     </row>
     <row r="1908">
@@ -49626,7 +49626,7 @@
         <v>1</v>
       </c>
       <c r="G1911" t="n">
-        <v>0.0459770114942529</v>
+        <v>0.0584707646176912</v>
       </c>
     </row>
     <row r="1912">
@@ -49691,7 +49691,7 @@
         <v>1</v>
       </c>
       <c r="G1914" t="n">
-        <v>0.298350824587706</v>
+        <v>0.305347326336832</v>
       </c>
     </row>
     <row r="1915">
@@ -49714,7 +49714,7 @@
         <v>1</v>
       </c>
       <c r="G1915" t="n">
-        <v>0.869565217391304</v>
+        <v>0.864567716141929</v>
       </c>
     </row>
     <row r="1916">
@@ -49802,7 +49802,7 @@
         <v>1</v>
       </c>
       <c r="G1919" t="n">
-        <v>0.178410794602699</v>
+        <v>0.185907046476762</v>
       </c>
     </row>
     <row r="1920">
@@ -49846,7 +49846,7 @@
         <v>1</v>
       </c>
       <c r="G1921" t="n">
-        <v>0.0149925037481259</v>
+        <v>0.0109945027486257</v>
       </c>
     </row>
     <row r="1922">
@@ -49869,7 +49869,7 @@
         <v>1</v>
       </c>
       <c r="G1922" t="n">
-        <v>0.0374812593703148</v>
+        <v>0.0294852573713143</v>
       </c>
     </row>
     <row r="1923">
@@ -49913,7 +49913,7 @@
         <v>1</v>
       </c>
       <c r="G1924" t="n">
-        <v>0.124437781109445</v>
+        <v>0.12143928035982</v>
       </c>
     </row>
     <row r="1925">
@@ -49936,7 +49936,7 @@
         <v>1</v>
       </c>
       <c r="G1925" t="n">
-        <v>0.580209895052474</v>
+        <v>0.588205897051474</v>
       </c>
     </row>
     <row r="1926">
@@ -49959,7 +49959,7 @@
         <v>1</v>
       </c>
       <c r="G1926" t="n">
-        <v>0.185407296351824</v>
+        <v>0.178410794602699</v>
       </c>
     </row>
     <row r="1927">
@@ -50003,7 +50003,7 @@
         <v>1</v>
       </c>
       <c r="G1928" t="n">
-        <v>0.262868565717141</v>
+        <v>0.256871564217891</v>
       </c>
     </row>
     <row r="1929">
@@ -50026,7 +50026,7 @@
         <v>1</v>
       </c>
       <c r="G1929" t="n">
-        <v>0.305847076461769</v>
+        <v>0.314842578710645</v>
       </c>
     </row>
     <row r="1930">
@@ -50072,7 +50072,7 @@
         <v>1</v>
       </c>
       <c r="G1931" t="n">
-        <v>0.00499750124937531</v>
+        <v>0.00599700149925037</v>
       </c>
     </row>
     <row r="1932">
@@ -50116,7 +50116,7 @@
         <v>1</v>
       </c>
       <c r="G1933" t="n">
-        <v>0.00199900049975012</v>
+        <v>0.00299850074962519</v>
       </c>
     </row>
     <row r="1934">
@@ -50183,7 +50183,7 @@
         <v>1</v>
       </c>
       <c r="G1936" t="n">
-        <v>0.0164917541229385</v>
+        <v>0.0114942528735632</v>
       </c>
     </row>
     <row r="1937">
@@ -50248,7 +50248,7 @@
         <v>1</v>
       </c>
       <c r="G1939" t="n">
-        <v>0.000499750124937531</v>
+        <v>0.00149925037481259</v>
       </c>
     </row>
     <row r="1940">
@@ -50336,7 +50336,7 @@
         <v>1</v>
       </c>
       <c r="G1943" t="n">
-        <v>0.743628185907046</v>
+        <v>0.735132433783108</v>
       </c>
     </row>
     <row r="1944">
@@ -50382,7 +50382,7 @@
         <v>1</v>
       </c>
       <c r="G1945" t="n">
-        <v>0.694652673663168</v>
+        <v>0.71264367816092</v>
       </c>
     </row>
     <row r="1946">
@@ -50447,7 +50447,7 @@
         <v>1</v>
       </c>
       <c r="G1948" t="n">
-        <v>0.0614692653673163</v>
+        <v>0.0549725137431284</v>
       </c>
     </row>
     <row r="1949">
@@ -50514,7 +50514,7 @@
         <v>1</v>
       </c>
       <c r="G1951" t="n">
-        <v>0.00199900049975012</v>
+        <v>0.00249875062468766</v>
       </c>
     </row>
     <row r="1952">
@@ -50537,7 +50537,7 @@
         <v>1</v>
       </c>
       <c r="G1952" t="n">
-        <v>0.00349825087456272</v>
+        <v>0.00249875062468766</v>
       </c>
     </row>
     <row r="1953">
@@ -50602,7 +50602,7 @@
         <v>1</v>
       </c>
       <c r="G1955" t="n">
-        <v>0.794602698650675</v>
+        <v>0.790604697651174</v>
       </c>
     </row>
     <row r="1956">
@@ -50646,7 +50646,7 @@
         <v>1</v>
       </c>
       <c r="G1957" t="n">
-        <v>0.00149925037481259</v>
+        <v>0.00199900049975012</v>
       </c>
     </row>
     <row r="1958">
@@ -50669,7 +50669,7 @@
         <v>1</v>
       </c>
       <c r="G1958" t="n">
-        <v>0.375812093953024</v>
+        <v>0.362818590704648</v>
       </c>
     </row>
     <row r="1959">
@@ -50692,7 +50692,7 @@
         <v>1</v>
       </c>
       <c r="G1959" t="n">
-        <v>0.00199900049975012</v>
+        <v>0.00449775112443778</v>
       </c>
     </row>
     <row r="1960">
@@ -50715,7 +50715,7 @@
         <v>1</v>
       </c>
       <c r="G1960" t="n">
-        <v>0.808595702148926</v>
+        <v>0.815092453773113</v>
       </c>
     </row>
     <row r="1961">
@@ -50759,7 +50759,7 @@
         <v>1</v>
       </c>
       <c r="G1962" t="n">
-        <v>0.128435782108946</v>
+        <v>0.133433283358321</v>
       </c>
     </row>
     <row r="1963">
@@ -50826,7 +50826,7 @@
         <v>1</v>
       </c>
       <c r="G1965" t="n">
-        <v>0.0424787606196902</v>
+        <v>0.0489755122438781</v>
       </c>
     </row>
     <row r="1966">
@@ -50849,7 +50849,7 @@
         <v>1</v>
       </c>
       <c r="G1966" t="n">
-        <v>0.0439780109945027</v>
+        <v>0.0469765117441279</v>
       </c>
     </row>
     <row r="1967">
@@ -50914,7 +50914,7 @@
         <v>1</v>
       </c>
       <c r="G1969" t="n">
-        <v>0.000499750124937531</v>
+        <v>0.000999500249875062</v>
       </c>
     </row>
     <row r="1970">
@@ -50937,7 +50937,7 @@
         <v>1</v>
       </c>
       <c r="G1970" t="n">
-        <v>0.0629685157421289</v>
+        <v>0.0624687656171914</v>
       </c>
     </row>
     <row r="1971">
@@ -50960,7 +50960,7 @@
         <v>1</v>
       </c>
       <c r="G1971" t="n">
-        <v>0.124937531234383</v>
+        <v>0.0999500249875062</v>
       </c>
     </row>
     <row r="1972">
@@ -50983,7 +50983,7 @@
         <v>1</v>
       </c>
       <c r="G1972" t="n">
-        <v>0.350324837581209</v>
+        <v>0.353823088455772</v>
       </c>
     </row>
     <row r="1973">
@@ -51006,7 +51006,7 @@
         <v>0</v>
       </c>
       <c r="G1973" t="n">
-        <v>0.000999500249875062</v>
+        <v>0.000499750124937531</v>
       </c>
     </row>
     <row r="1974">
@@ -51092,7 +51092,7 @@
         <v>0</v>
       </c>
       <c r="G1977" t="n">
-        <v>0.000499750124937531</v>
+        <v>0.000999500249875062</v>
       </c>
     </row>
     <row r="1978">
@@ -51157,7 +51157,7 @@
         <v>1</v>
       </c>
       <c r="G1980" t="n">
-        <v>0.0104947526236882</v>
+        <v>0.00949525237381309</v>
       </c>
     </row>
     <row r="1981">
@@ -51180,7 +51180,7 @@
         <v>1</v>
       </c>
       <c r="G1981" t="n">
-        <v>0.16191904047976</v>
+        <v>0.153423288355822</v>
       </c>
     </row>
     <row r="1982">
@@ -51203,7 +51203,7 @@
         <v>1</v>
       </c>
       <c r="G1982" t="n">
-        <v>0.231384307846077</v>
+        <v>0.24487756121939</v>
       </c>
     </row>
     <row r="1983">
@@ -51247,7 +51247,7 @@
         <v>1</v>
       </c>
       <c r="G1984" t="n">
-        <v>0.0164917541229385</v>
+        <v>0.0224887556221889</v>
       </c>
     </row>
     <row r="1985">
@@ -51291,7 +51291,7 @@
         <v>1</v>
       </c>
       <c r="G1986" t="n">
-        <v>0.477261369315342</v>
+        <v>0.493753123438281</v>
       </c>
     </row>
     <row r="1987">
@@ -51314,7 +51314,7 @@
         <v>1</v>
       </c>
       <c r="G1987" t="n">
-        <v>0.853573213393303</v>
+        <v>0.859070464767616</v>
       </c>
     </row>
     <row r="1988">
@@ -51337,7 +51337,7 @@
         <v>0</v>
       </c>
       <c r="G1988" t="n">
-        <v>0.00899550224887556</v>
+        <v>0.0064967516241879</v>
       </c>
     </row>
     <row r="1989">
@@ -51360,7 +51360,7 @@
         <v>1</v>
       </c>
       <c r="G1989" t="n">
-        <v>0.319340329835082</v>
+        <v>0.32583708145927</v>
       </c>
     </row>
     <row r="1990">
@@ -51406,7 +51406,7 @@
         <v>1</v>
       </c>
       <c r="G1991" t="n">
-        <v>0.0604697651174413</v>
+        <v>0.0659670164917541</v>
       </c>
     </row>
     <row r="1992">
@@ -51429,7 +51429,7 @@
         <v>1</v>
       </c>
       <c r="G1992" t="n">
-        <v>0.000999500249875062</v>
+        <v>0.000499750124937531</v>
       </c>
     </row>
     <row r="1993">
@@ -51496,7 +51496,7 @@
         <v>0</v>
       </c>
       <c r="G1995" t="n">
-        <v>0.000999500249875062</v>
+        <v>0.000499750124937531</v>
       </c>
     </row>
     <row r="1996">
@@ -51540,7 +51540,7 @@
         <v>1</v>
       </c>
       <c r="G1997" t="n">
-        <v>0.0204897551224388</v>
+        <v>0.0254872563718141</v>
       </c>
     </row>
     <row r="1998">
@@ -51607,7 +51607,7 @@
         <v>1</v>
       </c>
       <c r="G2000" t="n">
-        <v>0.00349825087456272</v>
+        <v>0.00249875062468766</v>
       </c>
     </row>
     <row r="2001">
@@ -51674,7 +51674,7 @@
         <v>1</v>
       </c>
       <c r="G2003" t="n">
-        <v>0.336331834082959</v>
+        <v>0.306346826586707</v>
       </c>
     </row>
     <row r="2004">
@@ -51697,7 +51697,7 @@
         <v>1</v>
       </c>
       <c r="G2004" t="n">
-        <v>0.235382308845577</v>
+        <v>0.221889055472264</v>
       </c>
     </row>
     <row r="2005">
@@ -51720,7 +51720,7 @@
         <v>0</v>
       </c>
       <c r="G2005" t="n">
-        <v>0.0359820089955022</v>
+        <v>0.0434782608695652</v>
       </c>
     </row>
     <row r="2006">
@@ -51743,7 +51743,7 @@
         <v>1</v>
       </c>
       <c r="G2006" t="n">
-        <v>0.000499750124937531</v>
+        <v>0.000999500249875062</v>
       </c>
     </row>
     <row r="2007">
@@ -51766,7 +51766,7 @@
         <v>1</v>
       </c>
       <c r="G2007" t="n">
-        <v>0.16391804097951</v>
+        <v>0.159420289855072</v>
       </c>
     </row>
     <row r="2008">
@@ -51831,7 +51831,7 @@
         <v>1</v>
       </c>
       <c r="G2010" t="n">
-        <v>0.23488255872064</v>
+        <v>0.250874562718641</v>
       </c>
     </row>
     <row r="2011">
@@ -51898,7 +51898,7 @@
         <v>1</v>
       </c>
       <c r="G2013" t="n">
-        <v>0.0134932533733133</v>
+        <v>0.0124937531234383</v>
       </c>
     </row>
     <row r="2014">
@@ -51921,7 +51921,7 @@
         <v>1</v>
       </c>
       <c r="G2014" t="n">
-        <v>0.106446776611694</v>
+        <v>0.129435282358821</v>
       </c>
     </row>
     <row r="2015">
@@ -51965,7 +51965,7 @@
         <v>1</v>
       </c>
       <c r="G2016" t="n">
-        <v>0.0514742628685657</v>
+        <v>0.047976011994003</v>
       </c>
     </row>
     <row r="2017">
@@ -51988,7 +51988,7 @@
         <v>1</v>
       </c>
       <c r="G2017" t="n">
-        <v>0.301349325337331</v>
+        <v>0.293853073463268</v>
       </c>
     </row>
     <row r="2018">
@@ -52011,7 +52011,7 @@
         <v>1</v>
       </c>
       <c r="G2018" t="n">
-        <v>0.375312343828086</v>
+        <v>0.397801099450275</v>
       </c>
     </row>
     <row r="2019">
@@ -52055,7 +52055,7 @@
         <v>1</v>
       </c>
       <c r="G2020" t="n">
-        <v>0.0104947526236882</v>
+        <v>0.00999500249875063</v>
       </c>
     </row>
     <row r="2021">
@@ -52078,7 +52078,7 @@
         <v>1</v>
       </c>
       <c r="G2021" t="n">
-        <v>0.750124937531234</v>
+        <v>0.729135432283858</v>
       </c>
     </row>
     <row r="2022">
@@ -52122,7 +52122,7 @@
         <v>1</v>
       </c>
       <c r="G2023" t="n">
-        <v>0.130934532733633</v>
+        <v>0.126936531734133</v>
       </c>
     </row>
     <row r="2024">
@@ -52145,7 +52145,7 @@
         <v>1</v>
       </c>
       <c r="G2024" t="n">
-        <v>0.0514742628685657</v>
+        <v>0.0609695152423788</v>
       </c>
     </row>
     <row r="2025">
@@ -52168,7 +52168,7 @@
         <v>1</v>
       </c>
       <c r="G2025" t="n">
-        <v>0.586706646676662</v>
+        <v>0.5992003998001</v>
       </c>
     </row>
     <row r="2026">
@@ -52191,7 +52191,7 @@
         <v>1</v>
       </c>
       <c r="G2026" t="n">
-        <v>0.015992003998001</v>
+        <v>0.0129935032483758</v>
       </c>
     </row>
     <row r="2027">
@@ -52300,7 +52300,7 @@
         <v>1</v>
       </c>
       <c r="G2031" t="n">
-        <v>0.610194902548726</v>
+        <v>0.624187906046976</v>
       </c>
     </row>
     <row r="2032">
@@ -52344,7 +52344,7 @@
         <v>0</v>
       </c>
       <c r="G2033" t="n">
-        <v>0.00449775112443778</v>
+        <v>0.00249875062468766</v>
       </c>
     </row>
     <row r="2034">
@@ -52388,7 +52388,7 @@
         <v>1</v>
       </c>
       <c r="G2035" t="n">
-        <v>0.0444777611194403</v>
+        <v>0.0429785107446277</v>
       </c>
     </row>
     <row r="2036">
@@ -52411,7 +52411,7 @@
         <v>1</v>
       </c>
       <c r="G2036" t="n">
-        <v>0.521739130434783</v>
+        <v>0.533233383308346</v>
       </c>
     </row>
     <row r="2037">
@@ -52455,7 +52455,7 @@
         <v>1</v>
       </c>
       <c r="G2038" t="n">
-        <v>0.180409795102449</v>
+        <v>0.173913043478261</v>
       </c>
     </row>
     <row r="2039">
@@ -52478,7 +52478,7 @@
         <v>1</v>
       </c>
       <c r="G2039" t="n">
-        <v>0.0979510244877561</v>
+        <v>0.0879560219890055</v>
       </c>
     </row>
     <row r="2040">
@@ -52545,7 +52545,7 @@
         <v>1</v>
       </c>
       <c r="G2042" t="n">
-        <v>0.0154922538730635</v>
+        <v>0.00999500249875063</v>
       </c>
     </row>
     <row r="2043">
@@ -52631,7 +52631,7 @@
         <v>1</v>
       </c>
       <c r="G2046" t="n">
-        <v>0.0124937531234383</v>
+        <v>0.00999500249875063</v>
       </c>
     </row>
     <row r="2047">
@@ -52677,7 +52677,7 @@
         <v>1</v>
       </c>
       <c r="G2048" t="n">
-        <v>0.000999500249875062</v>
+        <v>0.000499750124937531</v>
       </c>
     </row>
     <row r="2049">
@@ -52700,7 +52700,7 @@
         <v>1</v>
       </c>
       <c r="G2049" t="n">
-        <v>0.825587206396802</v>
+        <v>0.828085957021489</v>
       </c>
     </row>
     <row r="2050">
@@ -52744,7 +52744,7 @@
         <v>1</v>
       </c>
       <c r="G2051" t="n">
-        <v>0.594202898550725</v>
+        <v>0.600699650174913</v>
       </c>
     </row>
     <row r="2052">
@@ -52767,7 +52767,7 @@
         <v>1</v>
       </c>
       <c r="G2052" t="n">
-        <v>0.612693653173413</v>
+        <v>0.595702148925537</v>
       </c>
     </row>
     <row r="2053">
@@ -52790,7 +52790,7 @@
         <v>0</v>
       </c>
       <c r="G2053" t="n">
-        <v>0.0129935032483758</v>
+        <v>0.015992003998001</v>
       </c>
     </row>
     <row r="2054">
@@ -52813,7 +52813,7 @@
         <v>1</v>
       </c>
       <c r="G2054" t="n">
-        <v>0.0494752623688156</v>
+        <v>0.055472263868066</v>
       </c>
     </row>
     <row r="2055">
@@ -52857,7 +52857,7 @@
         <v>1</v>
       </c>
       <c r="G2056" t="n">
-        <v>0.811594202898551</v>
+        <v>0.835082458770615</v>
       </c>
     </row>
     <row r="2057">
@@ -52945,7 +52945,7 @@
         <v>0</v>
       </c>
       <c r="G2060" t="n">
-        <v>0.0304847576211894</v>
+        <v>0.0239880059970015</v>
       </c>
     </row>
     <row r="2061">
@@ -53033,7 +53033,7 @@
         <v>1</v>
       </c>
       <c r="G2064" t="n">
-        <v>0.00299850074962519</v>
+        <v>0.00199900049975012</v>
       </c>
     </row>
     <row r="2065">
@@ -53056,7 +53056,7 @@
         <v>0</v>
       </c>
       <c r="G2065" t="n">
-        <v>0.0464767616191904</v>
+        <v>0.04047976011994</v>
       </c>
     </row>
     <row r="2066">
@@ -53144,7 +53144,7 @@
         <v>0</v>
       </c>
       <c r="G2069" t="n">
-        <v>0.0379810094952524</v>
+        <v>0.031984007996002</v>
       </c>
     </row>
     <row r="2070">
@@ -53167,7 +53167,7 @@
         <v>1</v>
       </c>
       <c r="G2070" t="n">
-        <v>0.328335832083958</v>
+        <v>0.328835582208896</v>
       </c>
     </row>
     <row r="2071">
@@ -53211,7 +53211,7 @@
         <v>1</v>
       </c>
       <c r="G2072" t="n">
-        <v>0.0154922538730635</v>
+        <v>0.0199900049975013</v>
       </c>
     </row>
     <row r="2073">
@@ -53297,7 +53297,7 @@
         <v>1</v>
       </c>
       <c r="G2076" t="n">
-        <v>0.667666166916542</v>
+        <v>0.657671164417791</v>
       </c>
     </row>
     <row r="2077">
@@ -53364,7 +53364,7 @@
         <v>1</v>
       </c>
       <c r="G2079" t="n">
-        <v>0.0419790104947526</v>
+        <v>0.0459770114942529</v>
       </c>
     </row>
     <row r="2080">
@@ -53408,7 +53408,7 @@
         <v>1</v>
       </c>
       <c r="G2081" t="n">
-        <v>0.00349825087456272</v>
+        <v>0.00449775112443778</v>
       </c>
     </row>
     <row r="2082">
@@ -53452,7 +53452,7 @@
         <v>1</v>
       </c>
       <c r="G2083" t="n">
-        <v>0.0154922538730635</v>
+        <v>0.0179910044977511</v>
       </c>
     </row>
     <row r="2084">
@@ -53475,7 +53475,7 @@
         <v>1</v>
       </c>
       <c r="G2084" t="n">
-        <v>0.60519740129935</v>
+        <v>0.605697151424288</v>
       </c>
     </row>
     <row r="2085">
@@ -53628,7 +53628,7 @@
         <v>1</v>
       </c>
       <c r="G2091" t="n">
-        <v>0.307346326836582</v>
+        <v>0.318340829585207</v>
       </c>
     </row>
     <row r="2092">
@@ -53672,7 +53672,7 @@
         <v>1</v>
       </c>
       <c r="G2093" t="n">
-        <v>0.870064967516242</v>
+        <v>0.861569215392304</v>
       </c>
     </row>
     <row r="2094">
@@ -53739,7 +53739,7 @@
         <v>1</v>
       </c>
       <c r="G2096" t="n">
-        <v>0.605697151424288</v>
+        <v>0.60519740129935</v>
       </c>
     </row>
     <row r="2097">
@@ -53783,7 +53783,7 @@
         <v>1</v>
       </c>
       <c r="G2098" t="n">
-        <v>0.0329835082458771</v>
+        <v>0.031984007996002</v>
       </c>
     </row>
     <row r="2099">
@@ -53806,7 +53806,7 @@
         <v>1</v>
       </c>
       <c r="G2099" t="n">
-        <v>0.238380809595202</v>
+        <v>0.240379810094953</v>
       </c>
     </row>
     <row r="2100">
@@ -53850,7 +53850,7 @@
         <v>0</v>
       </c>
       <c r="G2101" t="n">
-        <v>0.152923538230885</v>
+        <v>0.15792103948026</v>
       </c>
     </row>
     <row r="2102">
@@ -53873,7 +53873,7 @@
         <v>1</v>
       </c>
       <c r="G2102" t="n">
-        <v>0.0224887556221889</v>
+        <v>0.0184907546226887</v>
       </c>
     </row>
     <row r="2103">
@@ -53896,7 +53896,7 @@
         <v>1</v>
       </c>
       <c r="G2103" t="n">
-        <v>0.00399800099950025</v>
+        <v>0.00249875062468766</v>
       </c>
     </row>
     <row r="2104">
@@ -53919,7 +53919,7 @@
         <v>1</v>
       </c>
       <c r="G2104" t="n">
-        <v>0.166416791604198</v>
+        <v>0.190404797601199</v>
       </c>
     </row>
     <row r="2105">
@@ -53963,7 +53963,7 @@
         <v>1</v>
       </c>
       <c r="G2106" t="n">
-        <v>0.308345827086457</v>
+        <v>0.309845077461269</v>
       </c>
     </row>
     <row r="2107">
@@ -53986,7 +53986,7 @@
         <v>1</v>
       </c>
       <c r="G2107" t="n">
-        <v>0.172413793103448</v>
+        <v>0.188405797101449</v>
       </c>
     </row>
     <row r="2108">
@@ -54009,7 +54009,7 @@
         <v>1</v>
       </c>
       <c r="G2108" t="n">
-        <v>0.864067966016992</v>
+        <v>0.848575712143928</v>
       </c>
     </row>
     <row r="2109">
@@ -54032,7 +54032,7 @@
         <v>0</v>
       </c>
       <c r="G2109" t="n">
-        <v>0.00549725137431284</v>
+        <v>0.00199900049975012</v>
       </c>
     </row>
     <row r="2110">
@@ -54118,7 +54118,7 @@
         <v>1</v>
       </c>
       <c r="G2113" t="n">
-        <v>0.331834082958521</v>
+        <v>0.301849075462269</v>
       </c>
     </row>
     <row r="2114">
@@ -54141,7 +54141,7 @@
         <v>1</v>
       </c>
       <c r="G2114" t="n">
-        <v>0.60519740129935</v>
+        <v>0.622188905547226</v>
       </c>
     </row>
     <row r="2115">
@@ -54164,7 +54164,7 @@
         <v>1</v>
       </c>
       <c r="G2115" t="n">
-        <v>0.00149925037481259</v>
+        <v>0.00249875062468766</v>
       </c>
     </row>
     <row r="2116">
@@ -54233,7 +54233,7 @@
         <v>1</v>
       </c>
       <c r="G2118" t="n">
-        <v>0.899550224887556</v>
+        <v>0.905547226386807</v>
       </c>
     </row>
     <row r="2119">
@@ -54319,7 +54319,7 @@
         <v>1</v>
       </c>
       <c r="G2122" t="n">
-        <v>0.0529735132433783</v>
+        <v>0.0604697651174413</v>
       </c>
     </row>
     <row r="2123">
@@ -54384,7 +54384,7 @@
         <v>1</v>
       </c>
       <c r="G2125" t="n">
-        <v>0.239880059970015</v>
+        <v>0.235382308845577</v>
       </c>
     </row>
     <row r="2126">
@@ -54407,7 +54407,7 @@
         <v>1</v>
       </c>
       <c r="G2126" t="n">
-        <v>0.000999500249875062</v>
+        <v>0.000499750124937531</v>
       </c>
     </row>
     <row r="2127">
@@ -54430,7 +54430,7 @@
         <v>1</v>
       </c>
       <c r="G2127" t="n">
-        <v>0.312343828085957</v>
+        <v>0.304347826086957</v>
       </c>
     </row>
     <row r="2128">
@@ -54453,7 +54453,7 @@
         <v>1</v>
       </c>
       <c r="G2128" t="n">
-        <v>0.134932533733133</v>
+        <v>0.144927536231884</v>
       </c>
     </row>
   </sheetData>
